--- a/Treasury_Calendar_Workbook.xlsx
+++ b/Treasury_Calendar_Workbook.xlsx
@@ -29,14 +29,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
     <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="168" formatCode="DD-MMM"/>
+    <numFmt numFmtId="167" formatCode="DD-MMM"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="169" formatCode="D"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,6 +136,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00B71C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -296,7 +302,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -381,11 +387,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001B365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="001B365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001B365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="001B365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001B365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -517,13 +576,13 @@
     <xf numFmtId="0" fontId="7" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -595,6 +654,32 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1056,6 +1141,9 @@
           <t>GENERAL SETTINGS</t>
         </is>
       </c>
+      <c r="B3" s="88" t="n"/>
+      <c r="C3" s="88" t="n"/>
+      <c r="D3" s="88" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1199,6 +1287,9 @@
           <t>CURRENCY CONFIGURATION</t>
         </is>
       </c>
+      <c r="B14" s="88" t="n"/>
+      <c r="C14" s="88" t="n"/>
+      <c r="D14" s="88" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1336,6 +1427,9 @@
           <t>PAYMENT STATUS CONFIGURATION</t>
         </is>
       </c>
+      <c r="B24" s="88" t="n"/>
+      <c r="C24" s="88" t="n"/>
+      <c r="D24" s="88" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -1485,6 +1579,9 @@
           <t>PAYMENT CATEGORIES</t>
         </is>
       </c>
+      <c r="B34" s="88" t="n"/>
+      <c r="C34" s="88" t="n"/>
+      <c r="D34" s="88" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -1694,6 +1791,9 @@
           <t>NAMED RANGES REFERENCE</t>
         </is>
       </c>
+      <c r="B47" s="88" t="n"/>
+      <c r="C47" s="88" t="n"/>
+      <c r="D47" s="88" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
@@ -1816,7 +1916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1938,10 +2038,8 @@
         <f>IFERROR((F4+G4)*VLOOKUP(E4,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="I4" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
+      <c r="I4" s="89" t="n">
+        <v>45646</v>
       </c>
       <c r="J4" s="37" t="n">
         <v>90</v>
@@ -1991,10 +2089,8 @@
         <f>IFERROR((F5+G5)*VLOOKUP(E5,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>2024-12-28</t>
-        </is>
+      <c r="I5" s="90" t="n">
+        <v>45654</v>
       </c>
       <c r="J5" s="8" t="n">
         <v>180</v>
@@ -2044,10 +2140,8 @@
         <f>IFERROR((F6+G6)*VLOOKUP(E6,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="I6" s="37" t="inlineStr">
-        <is>
-          <t>2025-01-15</t>
-        </is>
+      <c r="I6" s="89" t="n">
+        <v>45672</v>
       </c>
       <c r="J6" s="37" t="n">
         <v>60</v>
@@ -2097,10 +2191,8 @@
         <f>IFERROR((F7+G7)*VLOOKUP(E7,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>2025-01-30</t>
-        </is>
+      <c r="I7" s="90" t="n">
+        <v>45687</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>365</v>
@@ -2369,6 +2461,83 @@
       <c r="K22" s="35" t="n"/>
       <c r="L22" s="35" t="n"/>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -4845,7 +5014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5005,15 +5174,11 @@
         <f>IFERROR(H6*VLOOKUP(G6,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J6" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
-      </c>
-      <c r="K6" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
+      <c r="J6" s="31" t="n">
+        <v>45641</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>45641</v>
       </c>
       <c r="L6" s="47" t="inlineStr">
         <is>
@@ -5078,15 +5243,11 @@
         <f>IFERROR(H7*VLOOKUP(G7,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J7" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="K7" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
+      <c r="J7" s="34" t="n">
+        <v>45646</v>
+      </c>
+      <c r="K7" s="34" t="n">
+        <v>45646</v>
       </c>
       <c r="L7" s="48" t="inlineStr">
         <is>
@@ -5147,15 +5308,11 @@
         <f>IFERROR(H8*VLOOKUP(G8,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J8" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="K8" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-18</t>
-        </is>
+      <c r="J8" s="31" t="n">
+        <v>45644</v>
+      </c>
+      <c r="K8" s="31" t="n">
+        <v>45644</v>
       </c>
       <c r="L8" s="47" t="inlineStr">
         <is>
@@ -5220,25 +5377,19 @@
         <f>IFERROR(H9*VLOOKUP(G9,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J9" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-22</t>
-        </is>
-      </c>
-      <c r="K9" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-22</t>
-        </is>
+      <c r="J9" s="34" t="n">
+        <v>45648</v>
+      </c>
+      <c r="K9" s="34" t="n">
+        <v>45648</v>
       </c>
       <c r="L9" s="49" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="M9" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-10</t>
-        </is>
+      <c r="M9" s="34" t="n">
+        <v>45636</v>
       </c>
       <c r="N9" s="32" t="inlineStr">
         <is>
@@ -5293,15 +5444,11 @@
         <f>IFERROR(H10*VLOOKUP(G10,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J10" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="K10" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-25</t>
-        </is>
+      <c r="J10" s="31" t="n">
+        <v>45651</v>
+      </c>
+      <c r="K10" s="31" t="n">
+        <v>45651</v>
       </c>
       <c r="L10" s="48" t="inlineStr">
         <is>
@@ -5366,15 +5513,11 @@
         <f>IFERROR(H11*VLOOKUP(G11,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J11" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
-      </c>
-      <c r="K11" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
+      <c r="J11" s="34" t="n">
+        <v>45641</v>
+      </c>
+      <c r="K11" s="34" t="n">
+        <v>45641</v>
       </c>
       <c r="L11" s="47" t="inlineStr">
         <is>
@@ -5439,15 +5582,11 @@
         <f>IFERROR(H12*VLOOKUP(G12,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J12" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="K12" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
+      <c r="J12" s="31" t="n">
+        <v>45646</v>
+      </c>
+      <c r="K12" s="31" t="n">
+        <v>45646</v>
       </c>
       <c r="L12" s="48" t="inlineStr">
         <is>
@@ -5512,15 +5651,11 @@
         <f>IFERROR(H13*VLOOKUP(G13,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J13" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="K13" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-15</t>
-        </is>
+      <c r="J13" s="34" t="n">
+        <v>45672</v>
+      </c>
+      <c r="K13" s="34" t="n">
+        <v>45672</v>
       </c>
       <c r="L13" s="48" t="inlineStr">
         <is>
@@ -5585,15 +5720,11 @@
         <f>IFERROR(H14*VLOOKUP(G14,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J14" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="K14" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
+      <c r="J14" s="31" t="n">
+        <v>45657</v>
+      </c>
+      <c r="K14" s="31" t="n">
+        <v>45657</v>
       </c>
       <c r="L14" s="47" t="inlineStr">
         <is>
@@ -5658,15 +5789,11 @@
         <f>IFERROR(H15*VLOOKUP(G15,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J15" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="K15" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
+      <c r="J15" s="34" t="n">
+        <v>45667</v>
+      </c>
+      <c r="K15" s="34" t="n">
+        <v>45667</v>
       </c>
       <c r="L15" s="47" t="inlineStr">
         <is>
@@ -5731,15 +5858,11 @@
         <f>IFERROR(H16*VLOOKUP(G16,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J16" s="29" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="K16" s="29" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+      <c r="J16" s="31" t="n">
+        <v>45662</v>
+      </c>
+      <c r="K16" s="31" t="n">
+        <v>45662</v>
       </c>
       <c r="L16" s="48" t="inlineStr">
         <is>
@@ -5804,15 +5927,11 @@
         <f>IFERROR(H17*VLOOKUP(G17,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J17" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="K17" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-28</t>
-        </is>
+      <c r="J17" s="34" t="n">
+        <v>45654</v>
+      </c>
+      <c r="K17" s="34" t="n">
+        <v>45654</v>
       </c>
       <c r="L17" s="48" t="inlineStr">
         <is>
@@ -5877,15 +5996,11 @@
         <f>IFERROR(H18*VLOOKUP(G18,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J18" s="29" t="inlineStr">
-        <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
-      <c r="K18" s="29" t="inlineStr">
-        <is>
-          <t>2025-01-20</t>
-        </is>
+      <c r="J18" s="31" t="n">
+        <v>45677</v>
+      </c>
+      <c r="K18" s="31" t="n">
+        <v>45677</v>
       </c>
       <c r="L18" s="47" t="inlineStr">
         <is>
@@ -5950,15 +6065,11 @@
         <f>IFERROR(H19*VLOOKUP(G19,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J19" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="K19" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+      <c r="J19" s="34" t="n">
+        <v>45662</v>
+      </c>
+      <c r="K19" s="34" t="n">
+        <v>45662</v>
       </c>
       <c r="L19" s="48" t="inlineStr">
         <is>
@@ -6023,15 +6134,11 @@
         <f>IFERROR(H20*VLOOKUP(G20,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J20" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
-      </c>
-      <c r="K20" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
+      <c r="J20" s="31" t="n">
+        <v>45641</v>
+      </c>
+      <c r="K20" s="31" t="n">
+        <v>45641</v>
       </c>
       <c r="L20" s="48" t="inlineStr">
         <is>
@@ -6096,15 +6203,11 @@
         <f>IFERROR(H21*VLOOKUP(G21,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J21" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="K21" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
+      <c r="J21" s="34" t="n">
+        <v>45646</v>
+      </c>
+      <c r="K21" s="34" t="n">
+        <v>45646</v>
       </c>
       <c r="L21" s="47" t="inlineStr">
         <is>
@@ -6169,15 +6272,11 @@
         <f>IFERROR(H22*VLOOKUP(G22,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J22" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="K22" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-28</t>
-        </is>
+      <c r="J22" s="31" t="n">
+        <v>45654</v>
+      </c>
+      <c r="K22" s="31" t="n">
+        <v>45654</v>
       </c>
       <c r="L22" s="48" t="inlineStr">
         <is>
@@ -6242,15 +6341,11 @@
         <f>IFERROR(H23*VLOOKUP(G23,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J23" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="K23" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+      <c r="J23" s="34" t="n">
+        <v>45662</v>
+      </c>
+      <c r="K23" s="34" t="n">
+        <v>45662</v>
       </c>
       <c r="L23" s="48" t="inlineStr">
         <is>
@@ -6315,15 +6410,11 @@
         <f>IFERROR(H24*VLOOKUP(G24,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J24" s="29" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="K24" s="29" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
+      <c r="J24" s="31" t="n">
+        <v>45658</v>
+      </c>
+      <c r="K24" s="31" t="n">
+        <v>45658</v>
       </c>
       <c r="L24" s="48" t="inlineStr">
         <is>
@@ -6388,15 +6479,11 @@
         <f>IFERROR(H25*VLOOKUP(G25,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J25" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="K25" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+      <c r="J25" s="34" t="n">
+        <v>45662</v>
+      </c>
+      <c r="K25" s="34" t="n">
+        <v>45662</v>
       </c>
       <c r="L25" s="48" t="inlineStr">
         <is>
@@ -6457,15 +6544,11 @@
         <f>IFERROR(H26*VLOOKUP(G26,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J26" s="29" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="K26" s="29" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
+      <c r="J26" s="31" t="n">
+        <v>45658</v>
+      </c>
+      <c r="K26" s="31" t="n">
+        <v>45658</v>
       </c>
       <c r="L26" s="47" t="inlineStr">
         <is>
@@ -6530,25 +6613,19 @@
         <f>IFERROR(H27*VLOOKUP(G27,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J27" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-10</t>
-        </is>
-      </c>
-      <c r="K27" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-10</t>
-        </is>
+      <c r="J27" s="34" t="n">
+        <v>45636</v>
+      </c>
+      <c r="K27" s="34" t="n">
+        <v>45636</v>
       </c>
       <c r="L27" s="49" t="inlineStr">
         <is>
           <t>PAID</t>
         </is>
       </c>
-      <c r="M27" s="32" t="inlineStr">
-        <is>
-          <t>2024-12-08</t>
-        </is>
+      <c r="M27" s="34" t="n">
+        <v>45634</v>
       </c>
       <c r="N27" s="32" t="inlineStr">
         <is>
@@ -6607,15 +6684,11 @@
         <f>IFERROR(H28*VLOOKUP(G28,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J28" s="29" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
-      </c>
-      <c r="K28" s="29" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+      <c r="J28" s="31" t="n">
+        <v>45662</v>
+      </c>
+      <c r="K28" s="31" t="n">
+        <v>45662</v>
       </c>
       <c r="L28" s="47" t="inlineStr">
         <is>
@@ -6680,15 +6753,11 @@
         <f>IFERROR(H29*VLOOKUP(G29,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J29" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
-      </c>
-      <c r="K29" s="32" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
+      <c r="J29" s="34" t="n">
+        <v>45667</v>
+      </c>
+      <c r="K29" s="34" t="n">
+        <v>45667</v>
       </c>
       <c r="L29" s="47" t="inlineStr">
         <is>
@@ -6753,15 +6822,11 @@
         <f>IFERROR(H30*VLOOKUP(G30,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="J30" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="K30" s="29" t="inlineStr">
-        <is>
-          <t>2024-12-30</t>
-        </is>
+      <c r="J30" s="31" t="n">
+        <v>45656</v>
+      </c>
+      <c r="K30" s="31" t="n">
+        <v>45656</v>
       </c>
       <c r="L30" s="50" t="inlineStr">
         <is>
@@ -7983,6 +8048,125 @@
       <c r="O80" s="35" t="n"/>
       <c r="P80" s="35" t="n"/>
     </row>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:L1"/>
@@ -8968,184 +9152,184 @@
       </c>
       <c r="B6" s="52" t="n"/>
       <c r="C6" s="53" t="n"/>
-      <c r="D6" s="59" t="n">
+      <c r="D6" s="91" t="n">
         <v>45627</v>
       </c>
-      <c r="E6" s="59" t="n">
+      <c r="E6" s="91" t="n">
         <v>45628</v>
       </c>
-      <c r="F6" s="59" t="n">
+      <c r="F6" s="91" t="n">
         <v>45629</v>
       </c>
-      <c r="G6" s="59" t="n">
+      <c r="G6" s="91" t="n">
         <v>45630</v>
       </c>
-      <c r="H6" s="59" t="n">
+      <c r="H6" s="91" t="n">
         <v>45631</v>
       </c>
-      <c r="I6" s="60" t="n">
+      <c r="I6" s="92" t="n">
         <v>45632</v>
       </c>
-      <c r="J6" s="61" t="n">
+      <c r="J6" s="93" t="n">
         <v>45633</v>
       </c>
-      <c r="K6" s="59" t="n">
+      <c r="K6" s="91" t="n">
         <v>45634</v>
       </c>
-      <c r="L6" s="59" t="n">
+      <c r="L6" s="91" t="n">
         <v>45635</v>
       </c>
-      <c r="M6" s="59" t="n">
+      <c r="M6" s="91" t="n">
         <v>45636</v>
       </c>
-      <c r="N6" s="59" t="n">
+      <c r="N6" s="91" t="n">
         <v>45637</v>
       </c>
-      <c r="O6" s="59" t="n">
+      <c r="O6" s="91" t="n">
         <v>45638</v>
       </c>
-      <c r="P6" s="60" t="n">
+      <c r="P6" s="92" t="n">
         <v>45639</v>
       </c>
-      <c r="Q6" s="61" t="n">
+      <c r="Q6" s="93" t="n">
         <v>45640</v>
       </c>
-      <c r="R6" s="59" t="n">
+      <c r="R6" s="91" t="n">
         <v>45641</v>
       </c>
-      <c r="S6" s="59" t="n">
+      <c r="S6" s="91" t="n">
         <v>45642</v>
       </c>
-      <c r="T6" s="59" t="n">
+      <c r="T6" s="91" t="n">
         <v>45643</v>
       </c>
-      <c r="U6" s="59" t="n">
+      <c r="U6" s="91" t="n">
         <v>45644</v>
       </c>
-      <c r="V6" s="59" t="n">
+      <c r="V6" s="91" t="n">
         <v>45645</v>
       </c>
-      <c r="W6" s="60" t="n">
+      <c r="W6" s="92" t="n">
         <v>45646</v>
       </c>
-      <c r="X6" s="61" t="n">
+      <c r="X6" s="93" t="n">
         <v>45647</v>
       </c>
-      <c r="Y6" s="59" t="n">
+      <c r="Y6" s="91" t="n">
         <v>45648</v>
       </c>
-      <c r="Z6" s="59" t="n">
+      <c r="Z6" s="91" t="n">
         <v>45649</v>
       </c>
-      <c r="AA6" s="59" t="n">
+      <c r="AA6" s="91" t="n">
         <v>45650</v>
       </c>
-      <c r="AB6" s="59" t="n">
+      <c r="AB6" s="91" t="n">
         <v>45651</v>
       </c>
-      <c r="AC6" s="59" t="n">
+      <c r="AC6" s="91" t="n">
         <v>45652</v>
       </c>
-      <c r="AD6" s="60" t="n">
+      <c r="AD6" s="92" t="n">
         <v>45653</v>
       </c>
-      <c r="AE6" s="61" t="n">
+      <c r="AE6" s="93" t="n">
         <v>45654</v>
       </c>
-      <c r="AF6" s="59" t="n">
+      <c r="AF6" s="91" t="n">
         <v>45655</v>
       </c>
-      <c r="AG6" s="59" t="n">
+      <c r="AG6" s="91" t="n">
         <v>45656</v>
       </c>
-      <c r="AH6" s="59" t="n">
+      <c r="AH6" s="91" t="n">
         <v>45657</v>
       </c>
-      <c r="AI6" s="59" t="n">
+      <c r="AI6" s="91" t="n">
         <v>45658</v>
       </c>
-      <c r="AJ6" s="59" t="n">
+      <c r="AJ6" s="91" t="n">
         <v>45659</v>
       </c>
-      <c r="AK6" s="60" t="n">
+      <c r="AK6" s="92" t="n">
         <v>45660</v>
       </c>
-      <c r="AL6" s="61" t="n">
+      <c r="AL6" s="93" t="n">
         <v>45661</v>
       </c>
-      <c r="AM6" s="59" t="n">
+      <c r="AM6" s="91" t="n">
         <v>45662</v>
       </c>
-      <c r="AN6" s="59" t="n">
+      <c r="AN6" s="91" t="n">
         <v>45663</v>
       </c>
-      <c r="AO6" s="59" t="n">
+      <c r="AO6" s="91" t="n">
         <v>45664</v>
       </c>
-      <c r="AP6" s="59" t="n">
+      <c r="AP6" s="91" t="n">
         <v>45665</v>
       </c>
-      <c r="AQ6" s="59" t="n">
+      <c r="AQ6" s="91" t="n">
         <v>45666</v>
       </c>
-      <c r="AR6" s="60" t="n">
+      <c r="AR6" s="92" t="n">
         <v>45667</v>
       </c>
-      <c r="AS6" s="61" t="n">
+      <c r="AS6" s="93" t="n">
         <v>45668</v>
       </c>
-      <c r="AT6" s="59" t="n">
+      <c r="AT6" s="91" t="n">
         <v>45669</v>
       </c>
-      <c r="AU6" s="59" t="n">
+      <c r="AU6" s="91" t="n">
         <v>45670</v>
       </c>
-      <c r="AV6" s="59" t="n">
+      <c r="AV6" s="91" t="n">
         <v>45671</v>
       </c>
-      <c r="AW6" s="59" t="n">
+      <c r="AW6" s="91" t="n">
         <v>45672</v>
       </c>
-      <c r="AX6" s="59" t="n">
+      <c r="AX6" s="91" t="n">
         <v>45673</v>
       </c>
-      <c r="AY6" s="60" t="n">
+      <c r="AY6" s="92" t="n">
         <v>45674</v>
       </c>
-      <c r="AZ6" s="61" t="n">
+      <c r="AZ6" s="93" t="n">
         <v>45675</v>
       </c>
-      <c r="BA6" s="59" t="n">
+      <c r="BA6" s="91" t="n">
         <v>45676</v>
       </c>
-      <c r="BB6" s="59" t="n">
+      <c r="BB6" s="91" t="n">
         <v>45677</v>
       </c>
-      <c r="BC6" s="59" t="n">
+      <c r="BC6" s="91" t="n">
         <v>45678</v>
       </c>
-      <c r="BD6" s="59" t="n">
+      <c r="BD6" s="91" t="n">
         <v>45679</v>
       </c>
-      <c r="BE6" s="59" t="n">
+      <c r="BE6" s="91" t="n">
         <v>45680</v>
       </c>
-      <c r="BF6" s="60" t="n">
+      <c r="BF6" s="92" t="n">
         <v>45681</v>
       </c>
-      <c r="BG6" s="61" t="n">
+      <c r="BG6" s="93" t="n">
         <v>45682</v>
       </c>
-      <c r="BH6" s="59" t="n">
+      <c r="BH6" s="91" t="n">
         <v>45683</v>
       </c>
-      <c r="BI6" s="59" t="n">
+      <c r="BI6" s="91" t="n">
         <v>45684</v>
       </c>
-      <c r="BJ6" s="59" t="n">
+      <c r="BJ6" s="91" t="n">
         <v>45685</v>
       </c>
-      <c r="BK6" s="59" t="n">
+      <c r="BK6" s="91" t="n">
         <v>45686</v>
       </c>
     </row>
@@ -9529,6 +9713,8 @@
           <t>OPENING BALANCE</t>
         </is>
       </c>
+      <c r="B9" s="94" t="n"/>
+      <c r="C9" s="95" t="n"/>
       <c r="D9" s="67" t="n"/>
       <c r="E9" s="67" t="n"/>
       <c r="F9" s="67" t="n"/>
@@ -9596,6 +9782,8 @@
           <t xml:space="preserve">  Opening Cash Position (SAR)</t>
         </is>
       </c>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="53" t="n"/>
       <c r="D10" s="69" t="n">
         <v>5000000</v>
       </c>
@@ -9842,6 +10030,8 @@
           <t>INFLOWS</t>
         </is>
       </c>
+      <c r="B11" s="94" t="n"/>
+      <c r="C11" s="95" t="n"/>
       <c r="D11" s="67" t="n"/>
       <c r="E11" s="67" t="n"/>
       <c r="F11" s="67" t="n"/>
@@ -9909,6 +10099,8 @@
           <t xml:space="preserve">  Expected Collections</t>
         </is>
       </c>
+      <c r="B12" s="52" t="n"/>
+      <c r="C12" s="53" t="n"/>
       <c r="D12" s="70">
         <f>IFERROR(SUMIF(SRC_Collections.$H$4:$H$500,D$6,SRC_Collections.$G$4:$G$500),0)</f>
         <v/>
@@ -10156,6 +10348,8 @@
           <t xml:space="preserve">  Deposit Maturities</t>
         </is>
       </c>
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="53" t="n"/>
       <c r="D13" s="70">
         <f>IFERROR(SUMIF(SRC_Deposits.$I$4:$I$500,D$6,SRC_Deposits.$H$4:$H$500),0)</f>
         <v/>
@@ -10403,6 +10597,8 @@
           <t xml:space="preserve">  Other Inflows</t>
         </is>
       </c>
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="53" t="n"/>
       <c r="D14" s="69" t="n">
         <v>0</v>
       </c>
@@ -10590,6 +10786,8 @@
           <t xml:space="preserve">  TOTAL INFLOWS</t>
         </is>
       </c>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="53" t="n"/>
       <c r="D15" s="74">
         <f>IFERROR(D12+D13+D14,0)</f>
         <v/>
@@ -10837,6 +11035,8 @@
           <t>OUTFLOWS</t>
         </is>
       </c>
+      <c r="B16" s="94" t="n"/>
+      <c r="C16" s="95" t="n"/>
       <c r="D16" s="67" t="n"/>
       <c r="E16" s="67" t="n"/>
       <c r="F16" s="67" t="n"/>
@@ -10904,6 +11104,8 @@
           <t xml:space="preserve">  Operating Expenditures (OPeX)</t>
         </is>
       </c>
+      <c r="B17" s="52" t="n"/>
+      <c r="C17" s="53" t="n"/>
       <c r="D17" s="70">
         <f>IFERROR(SUMIF(SRC_OPeX.$H$4:$H$500,D$6,SRC_OPeX.$G$4:$G$500),0)</f>
         <v/>
@@ -11151,6 +11353,8 @@
           <t xml:space="preserve">  Capital Expenditures (CAPEX)</t>
         </is>
       </c>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="53" t="n"/>
       <c r="D18" s="70">
         <f>IFERROR(SUMIF(SRC_CAPEX.$H$4:$H$500,D$6,SRC_CAPEX.$G$4:$G$500),0)</f>
         <v/>
@@ -11398,6 +11602,8 @@
           <t xml:space="preserve">  Human Resources (Payroll)</t>
         </is>
       </c>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="53" t="n"/>
       <c r="D19" s="70">
         <f>IFERROR(SUMIF(SRC_HR.$H$4:$H$500,D$6,SRC_HR.$G$4:$G$500),0)</f>
         <v/>
@@ -11645,6 +11851,8 @@
           <t xml:space="preserve">  Debt Service &amp; Loans</t>
         </is>
       </c>
+      <c r="B20" s="52" t="n"/>
+      <c r="C20" s="53" t="n"/>
       <c r="D20" s="70">
         <f>IFERROR(SUMIF(SRC_Debt.$I$4:$I$500,D$6,SRC_Debt.$H$4:$H$500),0)</f>
         <v/>
@@ -11892,6 +12100,8 @@
           <t xml:space="preserve">  Fixed Expenses</t>
         </is>
       </c>
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="53" t="n"/>
       <c r="D21" s="70">
         <f>IFERROR(SUMIF(SRC_Fixed.$H$4:$H$500,D$6,SRC_Fixed.$G$4:$G$500),0)</f>
         <v/>
@@ -12139,6 +12349,8 @@
           <t xml:space="preserve">  Variable Expenses</t>
         </is>
       </c>
+      <c r="B22" s="52" t="n"/>
+      <c r="C22" s="53" t="n"/>
       <c r="D22" s="70">
         <f>IFERROR(SUMIF(SRC_Variable.$H$4:$H$500,D$6,SRC_Variable.$G$4:$G$500),0)</f>
         <v/>
@@ -12386,6 +12598,8 @@
           <t xml:space="preserve">  Payment Calendar Items</t>
         </is>
       </c>
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="53" t="n"/>
       <c r="D23" s="70">
         <f>IFERROR(SUMIF(Payment_Data.$J$6:$J$500,D$6,Payment_Data.$I$6:$I$500),0)</f>
         <v/>
@@ -12633,6 +12847,8 @@
           <t xml:space="preserve">  Other Outflows</t>
         </is>
       </c>
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="53" t="n"/>
       <c r="D24" s="69" t="n">
         <v>0</v>
       </c>
@@ -12820,6 +13036,8 @@
           <t xml:space="preserve">  TOTAL OUTFLOWS</t>
         </is>
       </c>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="53" t="n"/>
       <c r="D25" s="74">
         <f>IFERROR(D17+D18+D19+D20+D21+D22+D24,0)</f>
         <v/>
@@ -13067,6 +13285,8 @@
           <t>NET CASH FLOW</t>
         </is>
       </c>
+      <c r="B26" s="94" t="n"/>
+      <c r="C26" s="95" t="n"/>
       <c r="D26" s="67" t="n"/>
       <c r="E26" s="67" t="n"/>
       <c r="F26" s="67" t="n"/>
@@ -13134,6 +13354,8 @@
           <t xml:space="preserve">  Daily Net Position</t>
         </is>
       </c>
+      <c r="B27" s="52" t="n"/>
+      <c r="C27" s="53" t="n"/>
       <c r="D27" s="75">
         <f>IFERROR(D15-D25,0)</f>
         <v/>
@@ -13381,6 +13603,8 @@
           <t>CLOSING BALANCE</t>
         </is>
       </c>
+      <c r="B28" s="94" t="n"/>
+      <c r="C28" s="95" t="n"/>
       <c r="D28" s="67" t="n"/>
       <c r="E28" s="67" t="n"/>
       <c r="F28" s="67" t="n"/>
@@ -13448,6 +13672,8 @@
           <t xml:space="preserve">  Closing Cash Position (SAR)</t>
         </is>
       </c>
+      <c r="B29" s="52" t="n"/>
+      <c r="C29" s="53" t="n"/>
       <c r="D29" s="74">
         <f>IFERROR(D10+D27,0)</f>
         <v/>
@@ -13695,6 +13921,8 @@
           <t>CUMULATIVE ANALYSIS</t>
         </is>
       </c>
+      <c r="B30" s="94" t="n"/>
+      <c r="C30" s="95" t="n"/>
       <c r="D30" s="67" t="n"/>
       <c r="E30" s="67" t="n"/>
       <c r="F30" s="67" t="n"/>
@@ -13762,6 +13990,8 @@
           <t xml:space="preserve">  Cumulative Inflows</t>
         </is>
       </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="53" t="n"/>
       <c r="D31" s="70">
         <f>IFERROR(D15,0)</f>
         <v/>
@@ -14009,6 +14239,8 @@
           <t xml:space="preserve">  Cumulative Outflows</t>
         </is>
       </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="53" t="n"/>
       <c r="D32" s="70">
         <f>IFERROR(D25,0)</f>
         <v/>
@@ -14256,6 +14488,8 @@
           <t xml:space="preserve">  Running Balance</t>
         </is>
       </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="53" t="n"/>
       <c r="D33" s="75">
         <f>IFERROR(D29,0)</f>
         <v/>
@@ -14828,7 +15062,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="78" t="n"/>
+      <c r="A4" s="96" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
       <c r="B4" s="78" t="n"/>
       <c r="C4" s="78" t="n"/>
       <c r="D4" s="78" t="n"/>
@@ -15134,7 +15372,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
+      <c r="A5" s="96" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
       <c r="B5" s="78" t="n"/>
       <c r="C5" s="78" t="n"/>
       <c r="D5" s="78" t="n"/>
@@ -15320,193 +15562,201 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="78" t="n"/>
+      <c r="A6" s="96" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
       <c r="B6" s="78" t="n"/>
       <c r="C6" s="78" t="n"/>
       <c r="D6" s="78" t="n"/>
-      <c r="E6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="57" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" s="58" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="P6" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q6" s="57" t="n">
-        <v>13</v>
-      </c>
-      <c r="R6" s="58" t="n">
-        <v>14</v>
-      </c>
-      <c r="S6" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="T6" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="U6" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="V6" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="W6" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="X6" s="57" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y6" s="58" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z6" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA6" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB6" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC6" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD6" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE6" s="57" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF6" s="58" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG6" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH6" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI6" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="AJ6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL6" s="57" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM6" s="58" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO6" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP6" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ6" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR6" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS6" s="57" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT6" s="58" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU6" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV6" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW6" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX6" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY6" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ6" s="57" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA6" s="58" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB6" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC6" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD6" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE6" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BF6" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG6" s="57" t="n">
-        <v>24</v>
-      </c>
-      <c r="BH6" s="58" t="n">
-        <v>25</v>
-      </c>
-      <c r="BI6" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="BJ6" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="BK6" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BL6" s="7" t="n">
-        <v>29</v>
+      <c r="E6" s="97" t="n">
+        <v>45627</v>
+      </c>
+      <c r="F6" s="97" t="n">
+        <v>45628</v>
+      </c>
+      <c r="G6" s="97" t="n">
+        <v>45629</v>
+      </c>
+      <c r="H6" s="97" t="n">
+        <v>45630</v>
+      </c>
+      <c r="I6" s="97" t="n">
+        <v>45631</v>
+      </c>
+      <c r="J6" s="98" t="n">
+        <v>45632</v>
+      </c>
+      <c r="K6" s="99" t="n">
+        <v>45633</v>
+      </c>
+      <c r="L6" s="97" t="n">
+        <v>45634</v>
+      </c>
+      <c r="M6" s="97" t="n">
+        <v>45635</v>
+      </c>
+      <c r="N6" s="97" t="n">
+        <v>45636</v>
+      </c>
+      <c r="O6" s="97" t="n">
+        <v>45637</v>
+      </c>
+      <c r="P6" s="97" t="n">
+        <v>45638</v>
+      </c>
+      <c r="Q6" s="98" t="n">
+        <v>45639</v>
+      </c>
+      <c r="R6" s="99" t="n">
+        <v>45640</v>
+      </c>
+      <c r="S6" s="97" t="n">
+        <v>45641</v>
+      </c>
+      <c r="T6" s="97" t="n">
+        <v>45642</v>
+      </c>
+      <c r="U6" s="97" t="n">
+        <v>45643</v>
+      </c>
+      <c r="V6" s="97" t="n">
+        <v>45644</v>
+      </c>
+      <c r="W6" s="97" t="n">
+        <v>45645</v>
+      </c>
+      <c r="X6" s="98" t="n">
+        <v>45646</v>
+      </c>
+      <c r="Y6" s="99" t="n">
+        <v>45647</v>
+      </c>
+      <c r="Z6" s="97" t="n">
+        <v>45648</v>
+      </c>
+      <c r="AA6" s="97" t="n">
+        <v>45649</v>
+      </c>
+      <c r="AB6" s="97" t="n">
+        <v>45650</v>
+      </c>
+      <c r="AC6" s="97" t="n">
+        <v>45651</v>
+      </c>
+      <c r="AD6" s="97" t="n">
+        <v>45652</v>
+      </c>
+      <c r="AE6" s="98" t="n">
+        <v>45653</v>
+      </c>
+      <c r="AF6" s="99" t="n">
+        <v>45654</v>
+      </c>
+      <c r="AG6" s="97" t="n">
+        <v>45655</v>
+      </c>
+      <c r="AH6" s="97" t="n">
+        <v>45656</v>
+      </c>
+      <c r="AI6" s="97" t="n">
+        <v>45657</v>
+      </c>
+      <c r="AJ6" s="97" t="n">
+        <v>45658</v>
+      </c>
+      <c r="AK6" s="97" t="n">
+        <v>45659</v>
+      </c>
+      <c r="AL6" s="98" t="n">
+        <v>45660</v>
+      </c>
+      <c r="AM6" s="99" t="n">
+        <v>45661</v>
+      </c>
+      <c r="AN6" s="97" t="n">
+        <v>45662</v>
+      </c>
+      <c r="AO6" s="97" t="n">
+        <v>45663</v>
+      </c>
+      <c r="AP6" s="97" t="n">
+        <v>45664</v>
+      </c>
+      <c r="AQ6" s="97" t="n">
+        <v>45665</v>
+      </c>
+      <c r="AR6" s="97" t="n">
+        <v>45666</v>
+      </c>
+      <c r="AS6" s="98" t="n">
+        <v>45667</v>
+      </c>
+      <c r="AT6" s="99" t="n">
+        <v>45668</v>
+      </c>
+      <c r="AU6" s="97" t="n">
+        <v>45669</v>
+      </c>
+      <c r="AV6" s="97" t="n">
+        <v>45670</v>
+      </c>
+      <c r="AW6" s="97" t="n">
+        <v>45671</v>
+      </c>
+      <c r="AX6" s="97" t="n">
+        <v>45672</v>
+      </c>
+      <c r="AY6" s="97" t="n">
+        <v>45673</v>
+      </c>
+      <c r="AZ6" s="98" t="n">
+        <v>45674</v>
+      </c>
+      <c r="BA6" s="99" t="n">
+        <v>45675</v>
+      </c>
+      <c r="BB6" s="97" t="n">
+        <v>45676</v>
+      </c>
+      <c r="BC6" s="97" t="n">
+        <v>45677</v>
+      </c>
+      <c r="BD6" s="97" t="n">
+        <v>45678</v>
+      </c>
+      <c r="BE6" s="97" t="n">
+        <v>45679</v>
+      </c>
+      <c r="BF6" s="97" t="n">
+        <v>45680</v>
+      </c>
+      <c r="BG6" s="98" t="n">
+        <v>45681</v>
+      </c>
+      <c r="BH6" s="99" t="n">
+        <v>45682</v>
+      </c>
+      <c r="BI6" s="97" t="n">
+        <v>45683</v>
+      </c>
+      <c r="BJ6" s="97" t="n">
+        <v>45684</v>
+      </c>
+      <c r="BK6" s="97" t="n">
+        <v>45685</v>
+      </c>
+      <c r="BL6" s="97" t="n">
+        <v>45686</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="78" t="n"/>
+      <c r="A7" s="96" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
       <c r="B7" s="78" t="n"/>
       <c r="C7" s="78" t="n"/>
       <c r="D7" s="78" t="n"/>
@@ -15883,6 +16133,9 @@
           <t>VENDOR PAYMENTS</t>
         </is>
       </c>
+      <c r="B9" s="94" t="n"/>
+      <c r="C9" s="94" t="n"/>
+      <c r="D9" s="95" t="n"/>
       <c r="E9" s="67" t="n"/>
       <c r="F9" s="67" t="n"/>
       <c r="G9" s="67" t="n"/>
@@ -17255,6 +17508,9 @@
           <t>HUMAN RESOURCES</t>
         </is>
       </c>
+      <c r="B15" s="94" t="n"/>
+      <c r="C15" s="94" t="n"/>
+      <c r="D15" s="95" t="n"/>
       <c r="E15" s="67" t="n"/>
       <c r="F15" s="67" t="n"/>
       <c r="G15" s="67" t="n"/>
@@ -18627,6 +18883,9 @@
           <t>GOVERNMENT PAYMENTS</t>
         </is>
       </c>
+      <c r="B21" s="94" t="n"/>
+      <c r="C21" s="94" t="n"/>
+      <c r="D21" s="95" t="n"/>
       <c r="E21" s="67" t="n"/>
       <c r="F21" s="67" t="n"/>
       <c r="G21" s="67" t="n"/>
@@ -19477,6 +19736,9 @@
           <t>STRATEGIC PAYMENTS</t>
         </is>
       </c>
+      <c r="B25" s="94" t="n"/>
+      <c r="C25" s="94" t="n"/>
+      <c r="D25" s="95" t="n"/>
       <c r="E25" s="67" t="n"/>
       <c r="F25" s="67" t="n"/>
       <c r="G25" s="67" t="n"/>
@@ -20588,6 +20850,9 @@
           <t>LOAN REPAYMENTS</t>
         </is>
       </c>
+      <c r="B30" s="94" t="n"/>
+      <c r="C30" s="94" t="n"/>
+      <c r="D30" s="95" t="n"/>
       <c r="E30" s="67" t="n"/>
       <c r="F30" s="67" t="n"/>
       <c r="G30" s="67" t="n"/>
@@ -21960,6 +22225,9 @@
           <t>OPERATING EXPENSES</t>
         </is>
       </c>
+      <c r="B36" s="94" t="n"/>
+      <c r="C36" s="94" t="n"/>
+      <c r="D36" s="95" t="n"/>
       <c r="E36" s="67" t="n"/>
       <c r="F36" s="67" t="n"/>
       <c r="G36" s="67" t="n"/>
@@ -22810,6 +23078,9 @@
           <t>CATEGORY TOTALS</t>
         </is>
       </c>
+      <c r="B40" s="94" t="n"/>
+      <c r="C40" s="94" t="n"/>
+      <c r="D40" s="95" t="n"/>
       <c r="E40" s="67" t="n"/>
       <c r="F40" s="67" t="n"/>
       <c r="G40" s="67" t="n"/>
@@ -23482,7 +23753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23601,10 +23872,8 @@
         <f>IFERROR(F4*VLOOKUP(E4,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H4" s="31" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
+      <c r="H4" s="31" t="n">
+        <v>45641</v>
       </c>
       <c r="I4" s="28" t="inlineStr">
         <is>
@@ -23658,10 +23927,8 @@
         <f>IFERROR(F5*VLOOKUP(E5,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H5" s="34" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
+      <c r="H5" s="34" t="n">
+        <v>45646</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
@@ -23711,10 +23978,8 @@
         <f>IFERROR(F6*VLOOKUP(E6,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H6" s="31" t="inlineStr">
-        <is>
-          <t>2024-12-25</t>
-        </is>
+      <c r="H6" s="31" t="n">
+        <v>45651</v>
       </c>
       <c r="I6" s="28" t="inlineStr">
         <is>
@@ -23768,10 +24033,8 @@
         <f>IFERROR(F7*VLOOKUP(E7,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H7" s="34" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+      <c r="H7" s="34" t="n">
+        <v>45662</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
@@ -23825,10 +24088,8 @@
         <f>IFERROR(F8*VLOOKUP(E8,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H8" s="31" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
+      <c r="H8" s="31" t="n">
+        <v>45667</v>
       </c>
       <c r="I8" s="28" t="inlineStr">
         <is>
@@ -24185,6 +24446,77 @@
       <c r="K28" s="35" t="n"/>
       <c r="L28" s="35" t="n"/>
     </row>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -24199,7 +24531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24318,10 +24650,8 @@
         <f>IFERROR(F4*VLOOKUP(E4,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H4" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
+      <c r="H4" s="89" t="n">
+        <v>45641</v>
       </c>
       <c r="I4" s="37" t="inlineStr">
         <is>
@@ -24377,10 +24707,8 @@
         <f>IFERROR(F5*VLOOKUP(E5,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
+      <c r="H5" s="90" t="n">
+        <v>45646</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -24432,10 +24760,8 @@
         <f>IFERROR(F6*VLOOKUP(E6,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H6" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-25</t>
-        </is>
+      <c r="H6" s="89" t="n">
+        <v>45651</v>
       </c>
       <c r="I6" s="37" t="inlineStr">
         <is>
@@ -24491,10 +24817,8 @@
         <f>IFERROR(F7*VLOOKUP(E7,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
+      <c r="H7" s="90" t="n">
+        <v>45658</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
@@ -24550,10 +24874,8 @@
         <f>IFERROR(F8*VLOOKUP(E8,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H8" s="37" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+      <c r="H8" s="89" t="n">
+        <v>45662</v>
       </c>
       <c r="I8" s="37" t="inlineStr">
         <is>
@@ -24912,6 +25234,77 @@
       <c r="K28" s="35" t="n"/>
       <c r="L28" s="35" t="n"/>
     </row>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -24926,7 +25319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25045,10 +25438,8 @@
         <f>IFERROR(F4*VLOOKUP(E4,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H4" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-18</t>
-        </is>
+      <c r="H4" s="89" t="n">
+        <v>45644</v>
       </c>
       <c r="I4" s="37" t="inlineStr">
         <is>
@@ -25104,10 +25495,8 @@
         <f>IFERROR(F5*VLOOKUP(E5,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>2024-12-28</t>
-        </is>
+      <c r="H5" s="90" t="n">
+        <v>45654</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -25163,10 +25552,8 @@
         <f>IFERROR(F6*VLOOKUP(E6,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H6" s="37" t="inlineStr">
-        <is>
-          <t>2025-01-15</t>
-        </is>
+      <c r="H6" s="89" t="n">
+        <v>45672</v>
       </c>
       <c r="I6" s="37" t="inlineStr">
         <is>
@@ -25222,10 +25609,8 @@
         <f>IFERROR(F7*VLOOKUP(E7,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>2025-01-20</t>
-        </is>
+      <c r="H7" s="90" t="n">
+        <v>45677</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
@@ -25503,6 +25888,83 @@
       <c r="K22" s="35" t="n"/>
       <c r="L22" s="35" t="n"/>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -25517,7 +25979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25636,10 +26098,8 @@
         <f>IFERROR(F4*VLOOKUP(E4,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H4" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-25</t>
-        </is>
+      <c r="H4" s="89" t="n">
+        <v>45651</v>
       </c>
       <c r="I4" s="37" t="inlineStr">
         <is>
@@ -25693,10 +26153,8 @@
         <f>IFERROR(F5*VLOOKUP(E5,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
+      <c r="H5" s="90" t="n">
+        <v>45641</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -25750,10 +26208,8 @@
         <f>IFERROR(F6*VLOOKUP(E6,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H6" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
+      <c r="H6" s="89" t="n">
+        <v>45646</v>
       </c>
       <c r="I6" s="37" t="inlineStr">
         <is>
@@ -25807,10 +26263,8 @@
         <f>IFERROR(F7*VLOOKUP(E7,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+      <c r="H7" s="90" t="n">
+        <v>45662</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
@@ -25864,10 +26318,8 @@
         <f>IFERROR(F8*VLOOKUP(E8,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H8" s="37" t="inlineStr">
-        <is>
-          <t>2025-01-15</t>
-        </is>
+      <c r="H8" s="89" t="n">
+        <v>45672</v>
       </c>
       <c r="I8" s="37" t="inlineStr">
         <is>
@@ -25921,10 +26373,8 @@
         <f>IFERROR(F9*VLOOKUP(E9,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>2025-01-20</t>
-        </is>
+      <c r="H9" s="90" t="n">
+        <v>45677</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
@@ -26285,6 +26735,76 @@
       <c r="K29" s="35" t="n"/>
       <c r="L29" s="35" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -26299,7 +26819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26421,10 +26941,8 @@
         <f>IFERROR((F4+G4)*VLOOKUP(E4,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="I4" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
+      <c r="I4" s="89" t="n">
+        <v>45641</v>
       </c>
       <c r="J4" s="30" t="n">
         <v>4500000</v>
@@ -26434,10 +26952,8 @@
           <t>SCHEDULED</t>
         </is>
       </c>
-      <c r="L4" s="37" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
+      <c r="L4" s="89" t="n">
+        <v>46371</v>
       </c>
     </row>
     <row r="5">
@@ -26476,10 +26992,8 @@
         <f>IFERROR((F5+G5)*VLOOKUP(E5,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
+      <c r="I5" s="90" t="n">
+        <v>45646</v>
       </c>
       <c r="J5" s="33" t="n">
         <v>3200000</v>
@@ -26489,10 +27003,8 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>2027-06-20</t>
-        </is>
+      <c r="L5" s="90" t="n">
+        <v>46558</v>
       </c>
     </row>
     <row r="6">
@@ -26531,10 +27043,8 @@
         <f>IFERROR((F6+G6)*VLOOKUP(E6,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="I6" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-28</t>
-        </is>
+      <c r="I6" s="89" t="n">
+        <v>45654</v>
       </c>
       <c r="J6" s="30" t="n">
         <v>1800000</v>
@@ -26544,10 +27054,8 @@
           <t>SCHEDULED</t>
         </is>
       </c>
-      <c r="L6" s="37" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
-        </is>
+      <c r="L6" s="89" t="n">
+        <v>46019</v>
       </c>
     </row>
     <row r="7">
@@ -26586,10 +27094,8 @@
         <f>IFERROR((F7+G7)*VLOOKUP(E7,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+      <c r="I7" s="90" t="n">
+        <v>45662</v>
       </c>
       <c r="J7" s="33" t="n">
         <v>680000</v>
@@ -26599,10 +27105,8 @@
           <t>SCHEDULED</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
+      <c r="L7" s="90" t="n">
+        <v>46027</v>
       </c>
     </row>
     <row r="8">
@@ -26641,10 +27145,8 @@
         <f>IFERROR((F8+G8)*VLOOKUP(E8,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="I8" s="37" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
+      <c r="I8" s="89" t="n">
+        <v>45667</v>
       </c>
       <c r="J8" s="30" t="n">
         <v>2700000</v>
@@ -26654,10 +27156,8 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="L8" s="37" t="inlineStr">
-        <is>
-          <t>2025-07-10</t>
-        </is>
+      <c r="L8" s="89" t="n">
+        <v>45848</v>
       </c>
     </row>
     <row r="9">
@@ -26915,6 +27415,82 @@
       <c r="K23" s="35" t="n"/>
       <c r="L23" s="35" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -26929,7 +27505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27048,20 +27624,16 @@
         <f>IFERROR(F4*VLOOKUP(E4,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H4" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-01</t>
-        </is>
+      <c r="H4" s="89" t="n">
+        <v>45627</v>
       </c>
       <c r="I4" s="37" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="J4" s="37" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="J4" s="89" t="n">
+        <v>46022</v>
       </c>
       <c r="K4" s="37" t="inlineStr">
         <is>
@@ -27107,20 +27679,16 @@
         <f>IFERROR(F5*VLOOKUP(E5,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>2024-12-15</t>
-        </is>
+      <c r="H5" s="90" t="n">
+        <v>45641</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="J5" s="90" t="n">
+        <v>46022</v>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
@@ -27166,20 +27734,16 @@
         <f>IFERROR(F6*VLOOKUP(E6,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H6" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
+      <c r="H6" s="89" t="n">
+        <v>45646</v>
       </c>
       <c r="I6" s="37" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="J6" s="37" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
-        </is>
+      <c r="J6" s="89" t="n">
+        <v>45838</v>
       </c>
       <c r="K6" s="37" t="inlineStr">
         <is>
@@ -27225,20 +27789,16 @@
         <f>IFERROR(F7*VLOOKUP(E7,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>2024-12-25</t>
-        </is>
+      <c r="H7" s="90" t="n">
+        <v>45651</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
+      <c r="J7" s="90" t="n">
+        <v>46022</v>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
@@ -27506,6 +28066,83 @@
       <c r="K22" s="35" t="n"/>
       <c r="L22" s="35" t="n"/>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -27520,7 +28157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27639,10 +28276,8 @@
         <f>IFERROR(F4*VLOOKUP(E4,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H4" s="37" t="inlineStr">
-        <is>
-          <t>2024-12-18</t>
-        </is>
+      <c r="H4" s="89" t="n">
+        <v>45644</v>
       </c>
       <c r="I4" s="37" t="inlineStr">
         <is>
@@ -27698,10 +28333,8 @@
         <f>IFERROR(F5*VLOOKUP(E5,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>2024-12-22</t>
-        </is>
+      <c r="H5" s="90" t="n">
+        <v>45648</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -27757,10 +28390,8 @@
         <f>IFERROR(F6*VLOOKUP(E6,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H6" s="37" t="inlineStr">
-        <is>
-          <t>2025-01-05</t>
-        </is>
+      <c r="H6" s="89" t="n">
+        <v>45662</v>
       </c>
       <c r="I6" s="37" t="inlineStr">
         <is>
@@ -27816,10 +28447,8 @@
         <f>IFERROR(F7*VLOOKUP(E7,FX_Rates.$A$6:$B$11,2,0),0)</f>
         <v/>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
+      <c r="H7" s="90" t="n">
+        <v>45667</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
@@ -28182,6 +28811,78 @@
       <c r="K27" s="35" t="n"/>
       <c r="L27" s="35" t="n"/>
     </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>

--- a/Treasury_Calendar_Workbook.xlsx
+++ b/Treasury_Calendar_Workbook.xlsx
@@ -29,13 +29,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
     <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="167" formatCode="DD-MMM"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="169" formatCode="D"/>
+    <numFmt numFmtId="168" formatCode="D"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -302,7 +301,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -440,11 +439,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -672,20 +677,30 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="17" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="17" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="10">
     <dxf>
       <font>
         <b val="1"/>
@@ -754,6 +769,38 @@
         <patternFill patternType="solid">
           <fgColor rgb="00FFF9C4"/>
           <bgColor rgb="00FFF9C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00B8CCE4"/>
+          <bgColor rgb="00B8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF6B6B"/>
+          <bgColor rgb="00FF6B6B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E6E6E6"/>
+          <bgColor rgb="00E6E6E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1136,7 +1183,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="100" t="inlineStr">
         <is>
           <t>GENERAL SETTINGS</t>
         </is>
@@ -1282,7 +1329,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="100" t="inlineStr">
         <is>
           <t>CURRENCY CONFIGURATION</t>
         </is>
@@ -1422,7 +1469,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="100" t="inlineStr">
         <is>
           <t>PAYMENT STATUS CONFIGURATION</t>
         </is>
@@ -1574,7 +1621,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="100" t="inlineStr">
         <is>
           <t>PAYMENT CATEGORIES</t>
         </is>
@@ -1786,7 +1833,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="100" t="inlineStr">
         <is>
           <t>NAMED RANGES REFERENCE</t>
         </is>
@@ -1916,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2461,83 +2508,6 @@
       <c r="K22" s="35" t="n"/>
       <c r="L22" s="35" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -5014,7 +4984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P199"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5171,7 +5141,7 @@
         <v>45000</v>
       </c>
       <c r="I6" s="30">
-        <f>IFERROR(H6*VLOOKUP(G6,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H6*VLOOKUP(G6,FX_Rates.$A$6:$B$11,2,0),H6)</f>
         <v/>
       </c>
       <c r="J6" s="31" t="n">
@@ -5240,7 +5210,7 @@
         <v>15000</v>
       </c>
       <c r="I7" s="33">
-        <f>IFERROR(H7*VLOOKUP(G7,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H7*VLOOKUP(G7,FX_Rates.$A$6:$B$11,2,0),H7)</f>
         <v/>
       </c>
       <c r="J7" s="34" t="n">
@@ -5305,7 +5275,7 @@
         <v>250000</v>
       </c>
       <c r="I8" s="30">
-        <f>IFERROR(H8*VLOOKUP(G8,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H8*VLOOKUP(G8,FX_Rates.$A$6:$B$11,2,0),H8)</f>
         <v/>
       </c>
       <c r="J8" s="31" t="n">
@@ -5374,7 +5344,7 @@
         <v>8500</v>
       </c>
       <c r="I9" s="33">
-        <f>IFERROR(H9*VLOOKUP(G9,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H9*VLOOKUP(G9,FX_Rates.$A$6:$B$11,2,0),H9)</f>
         <v/>
       </c>
       <c r="J9" s="34" t="n">
@@ -5441,7 +5411,7 @@
         <v>2500000</v>
       </c>
       <c r="I10" s="30">
-        <f>IFERROR(H10*VLOOKUP(G10,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H10*VLOOKUP(G10,FX_Rates.$A$6:$B$11,2,0),H10)</f>
         <v/>
       </c>
       <c r="J10" s="31" t="n">
@@ -5510,7 +5480,7 @@
         <v>375000</v>
       </c>
       <c r="I11" s="33">
-        <f>IFERROR(H11*VLOOKUP(G11,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H11*VLOOKUP(G11,FX_Rates.$A$6:$B$11,2,0),H11)</f>
         <v/>
       </c>
       <c r="J11" s="34" t="n">
@@ -5579,7 +5549,7 @@
         <v>180000</v>
       </c>
       <c r="I12" s="30">
-        <f>IFERROR(H12*VLOOKUP(G12,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H12*VLOOKUP(G12,FX_Rates.$A$6:$B$11,2,0),H12)</f>
         <v/>
       </c>
       <c r="J12" s="31" t="n">
@@ -5648,7 +5618,7 @@
         <v>450000</v>
       </c>
       <c r="I13" s="33">
-        <f>IFERROR(H13*VLOOKUP(G13,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H13*VLOOKUP(G13,FX_Rates.$A$6:$B$11,2,0),H13)</f>
         <v/>
       </c>
       <c r="J13" s="34" t="n">
@@ -5717,7 +5687,7 @@
         <v>285000</v>
       </c>
       <c r="I14" s="30">
-        <f>IFERROR(H14*VLOOKUP(G14,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H14*VLOOKUP(G14,FX_Rates.$A$6:$B$11,2,0),H14)</f>
         <v/>
       </c>
       <c r="J14" s="31" t="n">
@@ -5786,7 +5756,7 @@
         <v>125000</v>
       </c>
       <c r="I15" s="33">
-        <f>IFERROR(H15*VLOOKUP(G15,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H15*VLOOKUP(G15,FX_Rates.$A$6:$B$11,2,0),H15)</f>
         <v/>
       </c>
       <c r="J15" s="34" t="n">
@@ -5855,7 +5825,7 @@
         <v>45000</v>
       </c>
       <c r="I16" s="30">
-        <f>IFERROR(H16*VLOOKUP(G16,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H16*VLOOKUP(G16,FX_Rates.$A$6:$B$11,2,0),H16)</f>
         <v/>
       </c>
       <c r="J16" s="31" t="n">
@@ -5924,7 +5894,7 @@
         <v>500000</v>
       </c>
       <c r="I17" s="33">
-        <f>IFERROR(H17*VLOOKUP(G17,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H17*VLOOKUP(G17,FX_Rates.$A$6:$B$11,2,0),H17)</f>
         <v/>
       </c>
       <c r="J17" s="34" t="n">
@@ -5993,7 +5963,7 @@
         <v>150000</v>
       </c>
       <c r="I18" s="30">
-        <f>IFERROR(H18*VLOOKUP(G18,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H18*VLOOKUP(G18,FX_Rates.$A$6:$B$11,2,0),H18)</f>
         <v/>
       </c>
       <c r="J18" s="31" t="n">
@@ -6062,7 +6032,7 @@
         <v>75000</v>
       </c>
       <c r="I19" s="33">
-        <f>IFERROR(H19*VLOOKUP(G19,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H19*VLOOKUP(G19,FX_Rates.$A$6:$B$11,2,0),H19)</f>
         <v/>
       </c>
       <c r="J19" s="34" t="n">
@@ -6131,7 +6101,7 @@
         <v>525000</v>
       </c>
       <c r="I20" s="30">
-        <f>IFERROR(H20*VLOOKUP(G20,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H20*VLOOKUP(G20,FX_Rates.$A$6:$B$11,2,0),H20)</f>
         <v/>
       </c>
       <c r="J20" s="31" t="n">
@@ -6200,7 +6170,7 @@
         <v>368000</v>
       </c>
       <c r="I21" s="33">
-        <f>IFERROR(H21*VLOOKUP(G21,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H21*VLOOKUP(G21,FX_Rates.$A$6:$B$11,2,0),H21)</f>
         <v/>
       </c>
       <c r="J21" s="34" t="n">
@@ -6269,7 +6239,7 @@
         <v>12500</v>
       </c>
       <c r="I22" s="30">
-        <f>IFERROR(H22*VLOOKUP(G22,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H22*VLOOKUP(G22,FX_Rates.$A$6:$B$11,2,0),H22)</f>
         <v/>
       </c>
       <c r="J22" s="31" t="n">
@@ -6338,7 +6308,7 @@
         <v>89200</v>
       </c>
       <c r="I23" s="33">
-        <f>IFERROR(H23*VLOOKUP(G23,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H23*VLOOKUP(G23,FX_Rates.$A$6:$B$11,2,0),H23)</f>
         <v/>
       </c>
       <c r="J23" s="34" t="n">
@@ -6407,7 +6377,7 @@
         <v>150000</v>
       </c>
       <c r="I24" s="30">
-        <f>IFERROR(H24*VLOOKUP(G24,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H24*VLOOKUP(G24,FX_Rates.$A$6:$B$11,2,0),H24)</f>
         <v/>
       </c>
       <c r="J24" s="31" t="n">
@@ -6476,7 +6446,7 @@
         <v>35000</v>
       </c>
       <c r="I25" s="33">
-        <f>IFERROR(H25*VLOOKUP(G25,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H25*VLOOKUP(G25,FX_Rates.$A$6:$B$11,2,0),H25)</f>
         <v/>
       </c>
       <c r="J25" s="34" t="n">
@@ -6541,7 +6511,7 @@
         <v>85000</v>
       </c>
       <c r="I26" s="30">
-        <f>IFERROR(H26*VLOOKUP(G26,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H26*VLOOKUP(G26,FX_Rates.$A$6:$B$11,2,0),H26)</f>
         <v/>
       </c>
       <c r="J26" s="31" t="n">
@@ -6610,7 +6580,7 @@
         <v>45000</v>
       </c>
       <c r="I27" s="33">
-        <f>IFERROR(H27*VLOOKUP(G27,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H27*VLOOKUP(G27,FX_Rates.$A$6:$B$11,2,0),H27)</f>
         <v/>
       </c>
       <c r="J27" s="34" t="n">
@@ -6681,7 +6651,7 @@
         <v>95000</v>
       </c>
       <c r="I28" s="30">
-        <f>IFERROR(H28*VLOOKUP(G28,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H28*VLOOKUP(G28,FX_Rates.$A$6:$B$11,2,0),H28)</f>
         <v/>
       </c>
       <c r="J28" s="31" t="n">
@@ -6750,7 +6720,7 @@
         <v>465000</v>
       </c>
       <c r="I29" s="33">
-        <f>IFERROR(H29*VLOOKUP(G29,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H29*VLOOKUP(G29,FX_Rates.$A$6:$B$11,2,0),H29)</f>
         <v/>
       </c>
       <c r="J29" s="34" t="n">
@@ -6819,7 +6789,7 @@
         <v>85000</v>
       </c>
       <c r="I30" s="30">
-        <f>IFERROR(H30*VLOOKUP(G30,FX_Rates.$A$6:$B$11,2,0),0)</f>
+        <f>IFERROR(H30*VLOOKUP(G30,FX_Rates.$A$6:$B$11,2,0),H30)</f>
         <v/>
       </c>
       <c r="J30" s="31" t="n">
@@ -8048,125 +8018,6 @@
       <c r="O80" s="35" t="n"/>
       <c r="P80" s="35" t="n"/>
     </row>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:L1"/>
@@ -9788,239 +9639,239 @@
         <v>5000000</v>
       </c>
       <c r="E10" s="70">
-        <f>IFERROR(D20,0)</f>
+        <f>D29</f>
         <v/>
       </c>
       <c r="F10" s="70">
-        <f>IFERROR(E20,0)</f>
+        <f>E29</f>
         <v/>
       </c>
       <c r="G10" s="70">
-        <f>IFERROR(F20,0)</f>
+        <f>F29</f>
         <v/>
       </c>
       <c r="H10" s="70">
-        <f>IFERROR(G20,0)</f>
+        <f>G29</f>
         <v/>
       </c>
       <c r="I10" s="71">
-        <f>IFERROR(H20,0)</f>
+        <f>H29</f>
         <v/>
       </c>
       <c r="J10" s="72">
-        <f>IFERROR(I20,0)</f>
+        <f>I29</f>
         <v/>
       </c>
       <c r="K10" s="70">
-        <f>IFERROR(J20,0)</f>
+        <f>J29</f>
         <v/>
       </c>
       <c r="L10" s="70">
-        <f>IFERROR(K20,0)</f>
+        <f>K29</f>
         <v/>
       </c>
       <c r="M10" s="70">
-        <f>IFERROR(L20,0)</f>
+        <f>L29</f>
         <v/>
       </c>
       <c r="N10" s="70">
-        <f>IFERROR(M20,0)</f>
+        <f>M29</f>
         <v/>
       </c>
       <c r="O10" s="70">
-        <f>IFERROR(N20,0)</f>
+        <f>N29</f>
         <v/>
       </c>
       <c r="P10" s="71">
-        <f>IFERROR(O20,0)</f>
+        <f>O29</f>
         <v/>
       </c>
       <c r="Q10" s="72">
-        <f>IFERROR(P20,0)</f>
+        <f>P29</f>
         <v/>
       </c>
       <c r="R10" s="70">
-        <f>IFERROR(Q20,0)</f>
+        <f>Q29</f>
         <v/>
       </c>
       <c r="S10" s="70">
-        <f>IFERROR(R20,0)</f>
+        <f>R29</f>
         <v/>
       </c>
       <c r="T10" s="70">
-        <f>IFERROR(S20,0)</f>
+        <f>S29</f>
         <v/>
       </c>
       <c r="U10" s="70">
-        <f>IFERROR(T20,0)</f>
+        <f>T29</f>
         <v/>
       </c>
       <c r="V10" s="70">
-        <f>IFERROR(U20,0)</f>
+        <f>U29</f>
         <v/>
       </c>
       <c r="W10" s="71">
-        <f>IFERROR(V20,0)</f>
+        <f>V29</f>
         <v/>
       </c>
       <c r="X10" s="72">
-        <f>IFERROR(W20,0)</f>
+        <f>W29</f>
         <v/>
       </c>
       <c r="Y10" s="70">
-        <f>IFERROR(X20,0)</f>
+        <f>X29</f>
         <v/>
       </c>
       <c r="Z10" s="70">
-        <f>IFERROR(Y20,0)</f>
+        <f>Y29</f>
         <v/>
       </c>
       <c r="AA10" s="70">
-        <f>IFERROR(Z20,0)</f>
+        <f>Z29</f>
         <v/>
       </c>
       <c r="AB10" s="70">
-        <f>IFERROR(AA20,0)</f>
+        <f>AA29</f>
         <v/>
       </c>
       <c r="AC10" s="70">
-        <f>IFERROR(AB20,0)</f>
+        <f>AB29</f>
         <v/>
       </c>
       <c r="AD10" s="71">
-        <f>IFERROR(AC20,0)</f>
+        <f>AC29</f>
         <v/>
       </c>
       <c r="AE10" s="72">
-        <f>IFERROR(AD20,0)</f>
+        <f>AD29</f>
         <v/>
       </c>
       <c r="AF10" s="70">
-        <f>IFERROR(AE20,0)</f>
+        <f>AE29</f>
         <v/>
       </c>
       <c r="AG10" s="70">
-        <f>IFERROR(AF20,0)</f>
+        <f>AF29</f>
         <v/>
       </c>
       <c r="AH10" s="70">
-        <f>IFERROR(AG20,0)</f>
+        <f>AG29</f>
         <v/>
       </c>
       <c r="AI10" s="70">
-        <f>IFERROR(AH20,0)</f>
+        <f>AH29</f>
         <v/>
       </c>
       <c r="AJ10" s="70">
-        <f>IFERROR(AI20,0)</f>
+        <f>AI29</f>
         <v/>
       </c>
       <c r="AK10" s="71">
-        <f>IFERROR(AJ20,0)</f>
+        <f>AJ29</f>
         <v/>
       </c>
       <c r="AL10" s="72">
-        <f>IFERROR(AK20,0)</f>
+        <f>AK29</f>
         <v/>
       </c>
       <c r="AM10" s="70">
-        <f>IFERROR(AL20,0)</f>
+        <f>AL29</f>
         <v/>
       </c>
       <c r="AN10" s="70">
-        <f>IFERROR(AM20,0)</f>
+        <f>AM29</f>
         <v/>
       </c>
       <c r="AO10" s="70">
-        <f>IFERROR(AN20,0)</f>
+        <f>AN29</f>
         <v/>
       </c>
       <c r="AP10" s="70">
-        <f>IFERROR(AO20,0)</f>
+        <f>AO29</f>
         <v/>
       </c>
       <c r="AQ10" s="70">
-        <f>IFERROR(AP20,0)</f>
+        <f>AP29</f>
         <v/>
       </c>
       <c r="AR10" s="71">
-        <f>IFERROR(AQ20,0)</f>
+        <f>AQ29</f>
         <v/>
       </c>
       <c r="AS10" s="72">
-        <f>IFERROR(AR20,0)</f>
+        <f>AR29</f>
         <v/>
       </c>
       <c r="AT10" s="70">
-        <f>IFERROR(AS20,0)</f>
+        <f>AS29</f>
         <v/>
       </c>
       <c r="AU10" s="70">
-        <f>IFERROR(AT20,0)</f>
+        <f>AT29</f>
         <v/>
       </c>
       <c r="AV10" s="70">
-        <f>IFERROR(AU20,0)</f>
+        <f>AU29</f>
         <v/>
       </c>
       <c r="AW10" s="70">
-        <f>IFERROR(AV20,0)</f>
+        <f>AV29</f>
         <v/>
       </c>
       <c r="AX10" s="70">
-        <f>IFERROR(AW20,0)</f>
+        <f>AW29</f>
         <v/>
       </c>
       <c r="AY10" s="71">
-        <f>IFERROR(AX20,0)</f>
+        <f>AX29</f>
         <v/>
       </c>
       <c r="AZ10" s="72">
-        <f>IFERROR(AY20,0)</f>
+        <f>AY29</f>
         <v/>
       </c>
       <c r="BA10" s="70">
-        <f>IFERROR(AZ20,0)</f>
+        <f>AZ29</f>
         <v/>
       </c>
       <c r="BB10" s="70">
-        <f>IFERROR(BA20,0)</f>
+        <f>BA29</f>
         <v/>
       </c>
       <c r="BC10" s="70">
-        <f>IFERROR(BB20,0)</f>
+        <f>BB29</f>
         <v/>
       </c>
       <c r="BD10" s="70">
-        <f>IFERROR(BC20,0)</f>
+        <f>BC29</f>
         <v/>
       </c>
       <c r="BE10" s="70">
-        <f>IFERROR(BD20,0)</f>
+        <f>BD29</f>
         <v/>
       </c>
       <c r="BF10" s="71">
-        <f>IFERROR(BE20,0)</f>
+        <f>BE29</f>
         <v/>
       </c>
       <c r="BG10" s="72">
-        <f>IFERROR(BF20,0)</f>
+        <f>BF29</f>
         <v/>
       </c>
       <c r="BH10" s="70">
-        <f>IFERROR(BG20,0)</f>
+        <f>BG29</f>
         <v/>
       </c>
       <c r="BI10" s="70">
-        <f>IFERROR(BH20,0)</f>
+        <f>BH29</f>
         <v/>
       </c>
       <c r="BJ10" s="70">
-        <f>IFERROR(BI20,0)</f>
+        <f>BI29</f>
         <v/>
       </c>
       <c r="BK10" s="70">
-        <f>IFERROR(BJ20,0)</f>
+        <f>BJ29</f>
         <v/>
       </c>
     </row>
@@ -10789,243 +10640,243 @@
       <c r="B15" s="52" t="n"/>
       <c r="C15" s="53" t="n"/>
       <c r="D15" s="74">
-        <f>IFERROR(D12+D13+D14,0)</f>
+        <f>SUM(D12:D14)</f>
         <v/>
       </c>
       <c r="E15" s="74">
-        <f>IFERROR(E12+E13+E14,0)</f>
+        <f>SUM(E12:E14)</f>
         <v/>
       </c>
       <c r="F15" s="74">
-        <f>IFERROR(F12+F13+F14,0)</f>
+        <f>SUM(F12:F14)</f>
         <v/>
       </c>
       <c r="G15" s="74">
-        <f>IFERROR(G12+G13+G14,0)</f>
+        <f>SUM(G12:G14)</f>
         <v/>
       </c>
       <c r="H15" s="74">
-        <f>IFERROR(H12+H13+H14,0)</f>
+        <f>SUM(H12:H14)</f>
         <v/>
       </c>
       <c r="I15" s="74">
-        <f>IFERROR(I12+I13+I14,0)</f>
+        <f>SUM(I12:I14)</f>
         <v/>
       </c>
       <c r="J15" s="74">
-        <f>IFERROR(J12+J13+J14,0)</f>
+        <f>SUM(J12:J14)</f>
         <v/>
       </c>
       <c r="K15" s="74">
-        <f>IFERROR(K12+K13+K14,0)</f>
+        <f>SUM(K12:K14)</f>
         <v/>
       </c>
       <c r="L15" s="74">
-        <f>IFERROR(L12+L13+L14,0)</f>
+        <f>SUM(L12:L14)</f>
         <v/>
       </c>
       <c r="M15" s="74">
-        <f>IFERROR(M12+M13+M14,0)</f>
+        <f>SUM(M12:M14)</f>
         <v/>
       </c>
       <c r="N15" s="74">
-        <f>IFERROR(N12+N13+N14,0)</f>
+        <f>SUM(N12:N14)</f>
         <v/>
       </c>
       <c r="O15" s="74">
-        <f>IFERROR(O12+O13+O14,0)</f>
+        <f>SUM(O12:O14)</f>
         <v/>
       </c>
       <c r="P15" s="74">
-        <f>IFERROR(P12+P13+P14,0)</f>
+        <f>SUM(P12:P14)</f>
         <v/>
       </c>
       <c r="Q15" s="74">
-        <f>IFERROR(Q12+Q13+Q14,0)</f>
+        <f>SUM(Q12:Q14)</f>
         <v/>
       </c>
       <c r="R15" s="74">
-        <f>IFERROR(R12+R13+R14,0)</f>
+        <f>SUM(R12:R14)</f>
         <v/>
       </c>
       <c r="S15" s="74">
-        <f>IFERROR(S12+S13+S14,0)</f>
+        <f>SUM(S12:S14)</f>
         <v/>
       </c>
       <c r="T15" s="74">
-        <f>IFERROR(T12+T13+T14,0)</f>
+        <f>SUM(T12:T14)</f>
         <v/>
       </c>
       <c r="U15" s="74">
-        <f>IFERROR(U12+U13+U14,0)</f>
+        <f>SUM(U12:U14)</f>
         <v/>
       </c>
       <c r="V15" s="74">
-        <f>IFERROR(V12+V13+V14,0)</f>
+        <f>SUM(V12:V14)</f>
         <v/>
       </c>
       <c r="W15" s="74">
-        <f>IFERROR(W12+W13+W14,0)</f>
+        <f>SUM(W12:W14)</f>
         <v/>
       </c>
       <c r="X15" s="74">
-        <f>IFERROR(X12+X13+X14,0)</f>
+        <f>SUM(X12:X14)</f>
         <v/>
       </c>
       <c r="Y15" s="74">
-        <f>IFERROR(Y12+Y13+Y14,0)</f>
+        <f>SUM(Y12:Y14)</f>
         <v/>
       </c>
       <c r="Z15" s="74">
-        <f>IFERROR(Z12+Z13+Z14,0)</f>
+        <f>SUM(Z12:Z14)</f>
         <v/>
       </c>
       <c r="AA15" s="74">
-        <f>IFERROR(AA12+AA13+AA14,0)</f>
+        <f>SUM(AA12:AA14)</f>
         <v/>
       </c>
       <c r="AB15" s="74">
-        <f>IFERROR(AB12+AB13+AB14,0)</f>
+        <f>SUM(AB12:AB14)</f>
         <v/>
       </c>
       <c r="AC15" s="74">
-        <f>IFERROR(AC12+AC13+AC14,0)</f>
+        <f>SUM(AC12:AC14)</f>
         <v/>
       </c>
       <c r="AD15" s="74">
-        <f>IFERROR(AD12+AD13+AD14,0)</f>
+        <f>SUM(AD12:AD14)</f>
         <v/>
       </c>
       <c r="AE15" s="74">
-        <f>IFERROR(AE12+AE13+AE14,0)</f>
+        <f>SUM(AE12:AE14)</f>
         <v/>
       </c>
       <c r="AF15" s="74">
-        <f>IFERROR(AF12+AF13+AF14,0)</f>
+        <f>SUM(AF12:AF14)</f>
         <v/>
       </c>
       <c r="AG15" s="74">
-        <f>IFERROR(AG12+AG13+AG14,0)</f>
+        <f>SUM(AG12:AG14)</f>
         <v/>
       </c>
       <c r="AH15" s="74">
-        <f>IFERROR(AH12+AH13+AH14,0)</f>
+        <f>SUM(AH12:AH14)</f>
         <v/>
       </c>
       <c r="AI15" s="74">
-        <f>IFERROR(AI12+AI13+AI14,0)</f>
+        <f>SUM(AI12:AI14)</f>
         <v/>
       </c>
       <c r="AJ15" s="74">
-        <f>IFERROR(AJ12+AJ13+AJ14,0)</f>
+        <f>SUM(AJ12:AJ14)</f>
         <v/>
       </c>
       <c r="AK15" s="74">
-        <f>IFERROR(AK12+AK13+AK14,0)</f>
+        <f>SUM(AK12:AK14)</f>
         <v/>
       </c>
       <c r="AL15" s="74">
-        <f>IFERROR(AL12+AL13+AL14,0)</f>
+        <f>SUM(AL12:AL14)</f>
         <v/>
       </c>
       <c r="AM15" s="74">
-        <f>IFERROR(AM12+AM13+AM14,0)</f>
+        <f>SUM(AM12:AM14)</f>
         <v/>
       </c>
       <c r="AN15" s="74">
-        <f>IFERROR(AN12+AN13+AN14,0)</f>
+        <f>SUM(AN12:AN14)</f>
         <v/>
       </c>
       <c r="AO15" s="74">
-        <f>IFERROR(AO12+AO13+AO14,0)</f>
+        <f>SUM(AO12:AO14)</f>
         <v/>
       </c>
       <c r="AP15" s="74">
-        <f>IFERROR(AP12+AP13+AP14,0)</f>
+        <f>SUM(AP12:AP14)</f>
         <v/>
       </c>
       <c r="AQ15" s="74">
-        <f>IFERROR(AQ12+AQ13+AQ14,0)</f>
+        <f>SUM(AQ12:AQ14)</f>
         <v/>
       </c>
       <c r="AR15" s="74">
-        <f>IFERROR(AR12+AR13+AR14,0)</f>
+        <f>SUM(AR12:AR14)</f>
         <v/>
       </c>
       <c r="AS15" s="74">
-        <f>IFERROR(AS12+AS13+AS14,0)</f>
+        <f>SUM(AS12:AS14)</f>
         <v/>
       </c>
       <c r="AT15" s="74">
-        <f>IFERROR(AT12+AT13+AT14,0)</f>
+        <f>SUM(AT12:AT14)</f>
         <v/>
       </c>
       <c r="AU15" s="74">
-        <f>IFERROR(AU12+AU13+AU14,0)</f>
+        <f>SUM(AU12:AU14)</f>
         <v/>
       </c>
       <c r="AV15" s="74">
-        <f>IFERROR(AV12+AV13+AV14,0)</f>
+        <f>SUM(AV12:AV14)</f>
         <v/>
       </c>
       <c r="AW15" s="74">
-        <f>IFERROR(AW12+AW13+AW14,0)</f>
+        <f>SUM(AW12:AW14)</f>
         <v/>
       </c>
       <c r="AX15" s="74">
-        <f>IFERROR(AX12+AX13+AX14,0)</f>
+        <f>SUM(AX12:AX14)</f>
         <v/>
       </c>
       <c r="AY15" s="74">
-        <f>IFERROR(AY12+AY13+AY14,0)</f>
+        <f>SUM(AY12:AY14)</f>
         <v/>
       </c>
       <c r="AZ15" s="74">
-        <f>IFERROR(AZ12+AZ13+AZ14,0)</f>
+        <f>SUM(AZ12:AZ14)</f>
         <v/>
       </c>
       <c r="BA15" s="74">
-        <f>IFERROR(BA12+BA13+BA14,0)</f>
+        <f>SUM(BA12:BA14)</f>
         <v/>
       </c>
       <c r="BB15" s="74">
-        <f>IFERROR(BB12+BB13+BB14,0)</f>
+        <f>SUM(BB12:BB14)</f>
         <v/>
       </c>
       <c r="BC15" s="74">
-        <f>IFERROR(BC12+BC13+BC14,0)</f>
+        <f>SUM(BC12:BC14)</f>
         <v/>
       </c>
       <c r="BD15" s="74">
-        <f>IFERROR(BD12+BD13+BD14,0)</f>
+        <f>SUM(BD12:BD14)</f>
         <v/>
       </c>
       <c r="BE15" s="74">
-        <f>IFERROR(BE12+BE13+BE14,0)</f>
+        <f>SUM(BE12:BE14)</f>
         <v/>
       </c>
       <c r="BF15" s="74">
-        <f>IFERROR(BF12+BF13+BF14,0)</f>
+        <f>SUM(BF12:BF14)</f>
         <v/>
       </c>
       <c r="BG15" s="74">
-        <f>IFERROR(BG12+BG13+BG14,0)</f>
+        <f>SUM(BG12:BG14)</f>
         <v/>
       </c>
       <c r="BH15" s="74">
-        <f>IFERROR(BH12+BH13+BH14,0)</f>
+        <f>SUM(BH12:BH14)</f>
         <v/>
       </c>
       <c r="BI15" s="74">
-        <f>IFERROR(BI12+BI13+BI14,0)</f>
+        <f>SUM(BI12:BI14)</f>
         <v/>
       </c>
       <c r="BJ15" s="74">
-        <f>IFERROR(BJ12+BJ13+BJ14,0)</f>
+        <f>SUM(BJ12:BJ14)</f>
         <v/>
       </c>
       <c r="BK15" s="74">
-        <f>IFERROR(BK12+BK13+BK14,0)</f>
+        <f>SUM(BK12:BK14)</f>
         <v/>
       </c>
     </row>
@@ -13039,243 +12890,243 @@
       <c r="B25" s="52" t="n"/>
       <c r="C25" s="53" t="n"/>
       <c r="D25" s="74">
-        <f>IFERROR(D17+D18+D19+D20+D21+D22+D24,0)</f>
+        <f>SUM(D17:D24)</f>
         <v/>
       </c>
       <c r="E25" s="74">
-        <f>IFERROR(E17+E18+E19+E20+E21+E22+E24,0)</f>
+        <f>SUM(E17:E24)</f>
         <v/>
       </c>
       <c r="F25" s="74">
-        <f>IFERROR(F17+F18+F19+F20+F21+F22+F24,0)</f>
+        <f>SUM(F17:F24)</f>
         <v/>
       </c>
       <c r="G25" s="74">
-        <f>IFERROR(G17+G18+G19+G20+G21+G22+G24,0)</f>
+        <f>SUM(G17:G24)</f>
         <v/>
       </c>
       <c r="H25" s="74">
-        <f>IFERROR(H17+H18+H19+H20+H21+H22+H24,0)</f>
+        <f>SUM(H17:H24)</f>
         <v/>
       </c>
       <c r="I25" s="74">
-        <f>IFERROR(I17+I18+I19+I20+I21+I22+I24,0)</f>
+        <f>SUM(I17:I24)</f>
         <v/>
       </c>
       <c r="J25" s="74">
-        <f>IFERROR(J17+J18+J19+J20+J21+J22+J24,0)</f>
+        <f>SUM(J17:J24)</f>
         <v/>
       </c>
       <c r="K25" s="74">
-        <f>IFERROR(K17+K18+K19+K20+K21+K22+K24,0)</f>
+        <f>SUM(K17:K24)</f>
         <v/>
       </c>
       <c r="L25" s="74">
-        <f>IFERROR(L17+L18+L19+L20+L21+L22+L24,0)</f>
+        <f>SUM(L17:L24)</f>
         <v/>
       </c>
       <c r="M25" s="74">
-        <f>IFERROR(M17+M18+M19+M20+M21+M22+M24,0)</f>
+        <f>SUM(M17:M24)</f>
         <v/>
       </c>
       <c r="N25" s="74">
-        <f>IFERROR(N17+N18+N19+N20+N21+N22+N24,0)</f>
+        <f>SUM(N17:N24)</f>
         <v/>
       </c>
       <c r="O25" s="74">
-        <f>IFERROR(O17+O18+O19+O20+O21+O22+O24,0)</f>
+        <f>SUM(O17:O24)</f>
         <v/>
       </c>
       <c r="P25" s="74">
-        <f>IFERROR(P17+P18+P19+P20+P21+P22+P24,0)</f>
+        <f>SUM(P17:P24)</f>
         <v/>
       </c>
       <c r="Q25" s="74">
-        <f>IFERROR(Q17+Q18+Q19+Q20+Q21+Q22+Q24,0)</f>
+        <f>SUM(Q17:Q24)</f>
         <v/>
       </c>
       <c r="R25" s="74">
-        <f>IFERROR(R17+R18+R19+R20+R21+R22+R24,0)</f>
+        <f>SUM(R17:R24)</f>
         <v/>
       </c>
       <c r="S25" s="74">
-        <f>IFERROR(S17+S18+S19+S20+S21+S22+S24,0)</f>
+        <f>SUM(S17:S24)</f>
         <v/>
       </c>
       <c r="T25" s="74">
-        <f>IFERROR(T17+T18+T19+T20+T21+T22+T24,0)</f>
+        <f>SUM(T17:T24)</f>
         <v/>
       </c>
       <c r="U25" s="74">
-        <f>IFERROR(U17+U18+U19+U20+U21+U22+U24,0)</f>
+        <f>SUM(U17:U24)</f>
         <v/>
       </c>
       <c r="V25" s="74">
-        <f>IFERROR(V17+V18+V19+V20+V21+V22+V24,0)</f>
+        <f>SUM(V17:V24)</f>
         <v/>
       </c>
       <c r="W25" s="74">
-        <f>IFERROR(W17+W18+W19+W20+W21+W22+W24,0)</f>
+        <f>SUM(W17:W24)</f>
         <v/>
       </c>
       <c r="X25" s="74">
-        <f>IFERROR(X17+X18+X19+X20+X21+X22+X24,0)</f>
+        <f>SUM(X17:X24)</f>
         <v/>
       </c>
       <c r="Y25" s="74">
-        <f>IFERROR(Y17+Y18+Y19+Y20+Y21+Y22+Y24,0)</f>
+        <f>SUM(Y17:Y24)</f>
         <v/>
       </c>
       <c r="Z25" s="74">
-        <f>IFERROR(Z17+Z18+Z19+Z20+Z21+Z22+Z24,0)</f>
+        <f>SUM(Z17:Z24)</f>
         <v/>
       </c>
       <c r="AA25" s="74">
-        <f>IFERROR(AA17+AA18+AA19+AA20+AA21+AA22+AA24,0)</f>
+        <f>SUM(AA17:AA24)</f>
         <v/>
       </c>
       <c r="AB25" s="74">
-        <f>IFERROR(AB17+AB18+AB19+AB20+AB21+AB22+AB24,0)</f>
+        <f>SUM(AB17:AB24)</f>
         <v/>
       </c>
       <c r="AC25" s="74">
-        <f>IFERROR(AC17+AC18+AC19+AC20+AC21+AC22+AC24,0)</f>
+        <f>SUM(AC17:AC24)</f>
         <v/>
       </c>
       <c r="AD25" s="74">
-        <f>IFERROR(AD17+AD18+AD19+AD20+AD21+AD22+AD24,0)</f>
+        <f>SUM(AD17:AD24)</f>
         <v/>
       </c>
       <c r="AE25" s="74">
-        <f>IFERROR(AE17+AE18+AE19+AE20+AE21+AE22+AE24,0)</f>
+        <f>SUM(AE17:AE24)</f>
         <v/>
       </c>
       <c r="AF25" s="74">
-        <f>IFERROR(AF17+AF18+AF19+AF20+AF21+AF22+AF24,0)</f>
+        <f>SUM(AF17:AF24)</f>
         <v/>
       </c>
       <c r="AG25" s="74">
-        <f>IFERROR(AG17+AG18+AG19+AG20+AG21+AG22+AG24,0)</f>
+        <f>SUM(AG17:AG24)</f>
         <v/>
       </c>
       <c r="AH25" s="74">
-        <f>IFERROR(AH17+AH18+AH19+AH20+AH21+AH22+AH24,0)</f>
+        <f>SUM(AH17:AH24)</f>
         <v/>
       </c>
       <c r="AI25" s="74">
-        <f>IFERROR(AI17+AI18+AI19+AI20+AI21+AI22+AI24,0)</f>
+        <f>SUM(AI17:AI24)</f>
         <v/>
       </c>
       <c r="AJ25" s="74">
-        <f>IFERROR(AJ17+AJ18+AJ19+AJ20+AJ21+AJ22+AJ24,0)</f>
+        <f>SUM(AJ17:AJ24)</f>
         <v/>
       </c>
       <c r="AK25" s="74">
-        <f>IFERROR(AK17+AK18+AK19+AK20+AK21+AK22+AK24,0)</f>
+        <f>SUM(AK17:AK24)</f>
         <v/>
       </c>
       <c r="AL25" s="74">
-        <f>IFERROR(AL17+AL18+AL19+AL20+AL21+AL22+AL24,0)</f>
+        <f>SUM(AL17:AL24)</f>
         <v/>
       </c>
       <c r="AM25" s="74">
-        <f>IFERROR(AM17+AM18+AM19+AM20+AM21+AM22+AM24,0)</f>
+        <f>SUM(AM17:AM24)</f>
         <v/>
       </c>
       <c r="AN25" s="74">
-        <f>IFERROR(AN17+AN18+AN19+AN20+AN21+AN22+AN24,0)</f>
+        <f>SUM(AN17:AN24)</f>
         <v/>
       </c>
       <c r="AO25" s="74">
-        <f>IFERROR(AO17+AO18+AO19+AO20+AO21+AO22+AO24,0)</f>
+        <f>SUM(AO17:AO24)</f>
         <v/>
       </c>
       <c r="AP25" s="74">
-        <f>IFERROR(AP17+AP18+AP19+AP20+AP21+AP22+AP24,0)</f>
+        <f>SUM(AP17:AP24)</f>
         <v/>
       </c>
       <c r="AQ25" s="74">
-        <f>IFERROR(AQ17+AQ18+AQ19+AQ20+AQ21+AQ22+AQ24,0)</f>
+        <f>SUM(AQ17:AQ24)</f>
         <v/>
       </c>
       <c r="AR25" s="74">
-        <f>IFERROR(AR17+AR18+AR19+AR20+AR21+AR22+AR24,0)</f>
+        <f>SUM(AR17:AR24)</f>
         <v/>
       </c>
       <c r="AS25" s="74">
-        <f>IFERROR(AS17+AS18+AS19+AS20+AS21+AS22+AS24,0)</f>
+        <f>SUM(AS17:AS24)</f>
         <v/>
       </c>
       <c r="AT25" s="74">
-        <f>IFERROR(AT17+AT18+AT19+AT20+AT21+AT22+AT24,0)</f>
+        <f>SUM(AT17:AT24)</f>
         <v/>
       </c>
       <c r="AU25" s="74">
-        <f>IFERROR(AU17+AU18+AU19+AU20+AU21+AU22+AU24,0)</f>
+        <f>SUM(AU17:AU24)</f>
         <v/>
       </c>
       <c r="AV25" s="74">
-        <f>IFERROR(AV17+AV18+AV19+AV20+AV21+AV22+AV24,0)</f>
+        <f>SUM(AV17:AV24)</f>
         <v/>
       </c>
       <c r="AW25" s="74">
-        <f>IFERROR(AW17+AW18+AW19+AW20+AW21+AW22+AW24,0)</f>
+        <f>SUM(AW17:AW24)</f>
         <v/>
       </c>
       <c r="AX25" s="74">
-        <f>IFERROR(AX17+AX18+AX19+AX20+AX21+AX22+AX24,0)</f>
+        <f>SUM(AX17:AX24)</f>
         <v/>
       </c>
       <c r="AY25" s="74">
-        <f>IFERROR(AY17+AY18+AY19+AY20+AY21+AY22+AY24,0)</f>
+        <f>SUM(AY17:AY24)</f>
         <v/>
       </c>
       <c r="AZ25" s="74">
-        <f>IFERROR(AZ17+AZ18+AZ19+AZ20+AZ21+AZ22+AZ24,0)</f>
+        <f>SUM(AZ17:AZ24)</f>
         <v/>
       </c>
       <c r="BA25" s="74">
-        <f>IFERROR(BA17+BA18+BA19+BA20+BA21+BA22+BA24,0)</f>
+        <f>SUM(BA17:BA24)</f>
         <v/>
       </c>
       <c r="BB25" s="74">
-        <f>IFERROR(BB17+BB18+BB19+BB20+BB21+BB22+BB24,0)</f>
+        <f>SUM(BB17:BB24)</f>
         <v/>
       </c>
       <c r="BC25" s="74">
-        <f>IFERROR(BC17+BC18+BC19+BC20+BC21+BC22+BC24,0)</f>
+        <f>SUM(BC17:BC24)</f>
         <v/>
       </c>
       <c r="BD25" s="74">
-        <f>IFERROR(BD17+BD18+BD19+BD20+BD21+BD22+BD24,0)</f>
+        <f>SUM(BD17:BD24)</f>
         <v/>
       </c>
       <c r="BE25" s="74">
-        <f>IFERROR(BE17+BE18+BE19+BE20+BE21+BE22+BE24,0)</f>
+        <f>SUM(BE17:BE24)</f>
         <v/>
       </c>
       <c r="BF25" s="74">
-        <f>IFERROR(BF17+BF18+BF19+BF20+BF21+BF22+BF24,0)</f>
+        <f>SUM(BF17:BF24)</f>
         <v/>
       </c>
       <c r="BG25" s="74">
-        <f>IFERROR(BG17+BG18+BG19+BG20+BG21+BG22+BG24,0)</f>
+        <f>SUM(BG17:BG24)</f>
         <v/>
       </c>
       <c r="BH25" s="74">
-        <f>IFERROR(BH17+BH18+BH19+BH20+BH21+BH22+BH24,0)</f>
+        <f>SUM(BH17:BH24)</f>
         <v/>
       </c>
       <c r="BI25" s="74">
-        <f>IFERROR(BI17+BI18+BI19+BI20+BI21+BI22+BI24,0)</f>
+        <f>SUM(BI17:BI24)</f>
         <v/>
       </c>
       <c r="BJ25" s="74">
-        <f>IFERROR(BJ17+BJ18+BJ19+BJ20+BJ21+BJ22+BJ24,0)</f>
+        <f>SUM(BJ17:BJ24)</f>
         <v/>
       </c>
       <c r="BK25" s="74">
-        <f>IFERROR(BK17+BK18+BK19+BK20+BK21+BK22+BK24,0)</f>
+        <f>SUM(BK17:BK24)</f>
         <v/>
       </c>
     </row>
@@ -13357,243 +13208,243 @@
       <c r="B27" s="52" t="n"/>
       <c r="C27" s="53" t="n"/>
       <c r="D27" s="75">
-        <f>IFERROR(D15-D25,0)</f>
+        <f>D15-D25</f>
         <v/>
       </c>
       <c r="E27" s="75">
-        <f>IFERROR(E15-E25,0)</f>
+        <f>E15-E25</f>
         <v/>
       </c>
       <c r="F27" s="75">
-        <f>IFERROR(F15-F25,0)</f>
+        <f>F15-F25</f>
         <v/>
       </c>
       <c r="G27" s="75">
-        <f>IFERROR(G15-G25,0)</f>
+        <f>G15-G25</f>
         <v/>
       </c>
       <c r="H27" s="75">
-        <f>IFERROR(H15-H25,0)</f>
+        <f>H15-H25</f>
         <v/>
       </c>
       <c r="I27" s="75">
-        <f>IFERROR(I15-I25,0)</f>
+        <f>I15-I25</f>
         <v/>
       </c>
       <c r="J27" s="75">
-        <f>IFERROR(J15-J25,0)</f>
+        <f>J15-J25</f>
         <v/>
       </c>
       <c r="K27" s="75">
-        <f>IFERROR(K15-K25,0)</f>
+        <f>K15-K25</f>
         <v/>
       </c>
       <c r="L27" s="75">
-        <f>IFERROR(L15-L25,0)</f>
+        <f>L15-L25</f>
         <v/>
       </c>
       <c r="M27" s="75">
-        <f>IFERROR(M15-M25,0)</f>
+        <f>M15-M25</f>
         <v/>
       </c>
       <c r="N27" s="75">
-        <f>IFERROR(N15-N25,0)</f>
+        <f>N15-N25</f>
         <v/>
       </c>
       <c r="O27" s="75">
-        <f>IFERROR(O15-O25,0)</f>
+        <f>O15-O25</f>
         <v/>
       </c>
       <c r="P27" s="75">
-        <f>IFERROR(P15-P25,0)</f>
+        <f>P15-P25</f>
         <v/>
       </c>
       <c r="Q27" s="75">
-        <f>IFERROR(Q15-Q25,0)</f>
+        <f>Q15-Q25</f>
         <v/>
       </c>
       <c r="R27" s="75">
-        <f>IFERROR(R15-R25,0)</f>
+        <f>R15-R25</f>
         <v/>
       </c>
       <c r="S27" s="75">
-        <f>IFERROR(S15-S25,0)</f>
+        <f>S15-S25</f>
         <v/>
       </c>
       <c r="T27" s="75">
-        <f>IFERROR(T15-T25,0)</f>
+        <f>T15-T25</f>
         <v/>
       </c>
       <c r="U27" s="75">
-        <f>IFERROR(U15-U25,0)</f>
+        <f>U15-U25</f>
         <v/>
       </c>
       <c r="V27" s="75">
-        <f>IFERROR(V15-V25,0)</f>
+        <f>V15-V25</f>
         <v/>
       </c>
       <c r="W27" s="75">
-        <f>IFERROR(W15-W25,0)</f>
+        <f>W15-W25</f>
         <v/>
       </c>
       <c r="X27" s="75">
-        <f>IFERROR(X15-X25,0)</f>
+        <f>X15-X25</f>
         <v/>
       </c>
       <c r="Y27" s="75">
-        <f>IFERROR(Y15-Y25,0)</f>
+        <f>Y15-Y25</f>
         <v/>
       </c>
       <c r="Z27" s="75">
-        <f>IFERROR(Z15-Z25,0)</f>
+        <f>Z15-Z25</f>
         <v/>
       </c>
       <c r="AA27" s="75">
-        <f>IFERROR(AA15-AA25,0)</f>
+        <f>AA15-AA25</f>
         <v/>
       </c>
       <c r="AB27" s="75">
-        <f>IFERROR(AB15-AB25,0)</f>
+        <f>AB15-AB25</f>
         <v/>
       </c>
       <c r="AC27" s="75">
-        <f>IFERROR(AC15-AC25,0)</f>
+        <f>AC15-AC25</f>
         <v/>
       </c>
       <c r="AD27" s="75">
-        <f>IFERROR(AD15-AD25,0)</f>
+        <f>AD15-AD25</f>
         <v/>
       </c>
       <c r="AE27" s="75">
-        <f>IFERROR(AE15-AE25,0)</f>
+        <f>AE15-AE25</f>
         <v/>
       </c>
       <c r="AF27" s="75">
-        <f>IFERROR(AF15-AF25,0)</f>
+        <f>AF15-AF25</f>
         <v/>
       </c>
       <c r="AG27" s="75">
-        <f>IFERROR(AG15-AG25,0)</f>
+        <f>AG15-AG25</f>
         <v/>
       </c>
       <c r="AH27" s="75">
-        <f>IFERROR(AH15-AH25,0)</f>
+        <f>AH15-AH25</f>
         <v/>
       </c>
       <c r="AI27" s="75">
-        <f>IFERROR(AI15-AI25,0)</f>
+        <f>AI15-AI25</f>
         <v/>
       </c>
       <c r="AJ27" s="75">
-        <f>IFERROR(AJ15-AJ25,0)</f>
+        <f>AJ15-AJ25</f>
         <v/>
       </c>
       <c r="AK27" s="75">
-        <f>IFERROR(AK15-AK25,0)</f>
+        <f>AK15-AK25</f>
         <v/>
       </c>
       <c r="AL27" s="75">
-        <f>IFERROR(AL15-AL25,0)</f>
+        <f>AL15-AL25</f>
         <v/>
       </c>
       <c r="AM27" s="75">
-        <f>IFERROR(AM15-AM25,0)</f>
+        <f>AM15-AM25</f>
         <v/>
       </c>
       <c r="AN27" s="75">
-        <f>IFERROR(AN15-AN25,0)</f>
+        <f>AN15-AN25</f>
         <v/>
       </c>
       <c r="AO27" s="75">
-        <f>IFERROR(AO15-AO25,0)</f>
+        <f>AO15-AO25</f>
         <v/>
       </c>
       <c r="AP27" s="75">
-        <f>IFERROR(AP15-AP25,0)</f>
+        <f>AP15-AP25</f>
         <v/>
       </c>
       <c r="AQ27" s="75">
-        <f>IFERROR(AQ15-AQ25,0)</f>
+        <f>AQ15-AQ25</f>
         <v/>
       </c>
       <c r="AR27" s="75">
-        <f>IFERROR(AR15-AR25,0)</f>
+        <f>AR15-AR25</f>
         <v/>
       </c>
       <c r="AS27" s="75">
-        <f>IFERROR(AS15-AS25,0)</f>
+        <f>AS15-AS25</f>
         <v/>
       </c>
       <c r="AT27" s="75">
-        <f>IFERROR(AT15-AT25,0)</f>
+        <f>AT15-AT25</f>
         <v/>
       </c>
       <c r="AU27" s="75">
-        <f>IFERROR(AU15-AU25,0)</f>
+        <f>AU15-AU25</f>
         <v/>
       </c>
       <c r="AV27" s="75">
-        <f>IFERROR(AV15-AV25,0)</f>
+        <f>AV15-AV25</f>
         <v/>
       </c>
       <c r="AW27" s="75">
-        <f>IFERROR(AW15-AW25,0)</f>
+        <f>AW15-AW25</f>
         <v/>
       </c>
       <c r="AX27" s="75">
-        <f>IFERROR(AX15-AX25,0)</f>
+        <f>AX15-AX25</f>
         <v/>
       </c>
       <c r="AY27" s="75">
-        <f>IFERROR(AY15-AY25,0)</f>
+        <f>AY15-AY25</f>
         <v/>
       </c>
       <c r="AZ27" s="75">
-        <f>IFERROR(AZ15-AZ25,0)</f>
+        <f>AZ15-AZ25</f>
         <v/>
       </c>
       <c r="BA27" s="75">
-        <f>IFERROR(BA15-BA25,0)</f>
+        <f>BA15-BA25</f>
         <v/>
       </c>
       <c r="BB27" s="75">
-        <f>IFERROR(BB15-BB25,0)</f>
+        <f>BB15-BB25</f>
         <v/>
       </c>
       <c r="BC27" s="75">
-        <f>IFERROR(BC15-BC25,0)</f>
+        <f>BC15-BC25</f>
         <v/>
       </c>
       <c r="BD27" s="75">
-        <f>IFERROR(BD15-BD25,0)</f>
+        <f>BD15-BD25</f>
         <v/>
       </c>
       <c r="BE27" s="75">
-        <f>IFERROR(BE15-BE25,0)</f>
+        <f>BE15-BE25</f>
         <v/>
       </c>
       <c r="BF27" s="75">
-        <f>IFERROR(BF15-BF25,0)</f>
+        <f>BF15-BF25</f>
         <v/>
       </c>
       <c r="BG27" s="75">
-        <f>IFERROR(BG15-BG25,0)</f>
+        <f>BG15-BG25</f>
         <v/>
       </c>
       <c r="BH27" s="75">
-        <f>IFERROR(BH15-BH25,0)</f>
+        <f>BH15-BH25</f>
         <v/>
       </c>
       <c r="BI27" s="75">
-        <f>IFERROR(BI15-BI25,0)</f>
+        <f>BI15-BI25</f>
         <v/>
       </c>
       <c r="BJ27" s="75">
-        <f>IFERROR(BJ15-BJ25,0)</f>
+        <f>BJ15-BJ25</f>
         <v/>
       </c>
       <c r="BK27" s="75">
-        <f>IFERROR(BK15-BK25,0)</f>
+        <f>BK15-BK25</f>
         <v/>
       </c>
     </row>
@@ -13675,243 +13526,243 @@
       <c r="B29" s="52" t="n"/>
       <c r="C29" s="53" t="n"/>
       <c r="D29" s="74">
-        <f>IFERROR(D10+D27,0)</f>
+        <f>D10+D27</f>
         <v/>
       </c>
       <c r="E29" s="74">
-        <f>IFERROR(E10+E27,0)</f>
+        <f>E10+E27</f>
         <v/>
       </c>
       <c r="F29" s="74">
-        <f>IFERROR(F10+F27,0)</f>
+        <f>F10+F27</f>
         <v/>
       </c>
       <c r="G29" s="74">
-        <f>IFERROR(G10+G27,0)</f>
+        <f>G10+G27</f>
         <v/>
       </c>
       <c r="H29" s="74">
-        <f>IFERROR(H10+H27,0)</f>
+        <f>H10+H27</f>
         <v/>
       </c>
       <c r="I29" s="74">
-        <f>IFERROR(I10+I27,0)</f>
+        <f>I10+I27</f>
         <v/>
       </c>
       <c r="J29" s="74">
-        <f>IFERROR(J10+J27,0)</f>
+        <f>J10+J27</f>
         <v/>
       </c>
       <c r="K29" s="74">
-        <f>IFERROR(K10+K27,0)</f>
+        <f>K10+K27</f>
         <v/>
       </c>
       <c r="L29" s="74">
-        <f>IFERROR(L10+L27,0)</f>
+        <f>L10+L27</f>
         <v/>
       </c>
       <c r="M29" s="74">
-        <f>IFERROR(M10+M27,0)</f>
+        <f>M10+M27</f>
         <v/>
       </c>
       <c r="N29" s="74">
-        <f>IFERROR(N10+N27,0)</f>
+        <f>N10+N27</f>
         <v/>
       </c>
       <c r="O29" s="74">
-        <f>IFERROR(O10+O27,0)</f>
+        <f>O10+O27</f>
         <v/>
       </c>
       <c r="P29" s="74">
-        <f>IFERROR(P10+P27,0)</f>
+        <f>P10+P27</f>
         <v/>
       </c>
       <c r="Q29" s="74">
-        <f>IFERROR(Q10+Q27,0)</f>
+        <f>Q10+Q27</f>
         <v/>
       </c>
       <c r="R29" s="74">
-        <f>IFERROR(R10+R27,0)</f>
+        <f>R10+R27</f>
         <v/>
       </c>
       <c r="S29" s="74">
-        <f>IFERROR(S10+S27,0)</f>
+        <f>S10+S27</f>
         <v/>
       </c>
       <c r="T29" s="74">
-        <f>IFERROR(T10+T27,0)</f>
+        <f>T10+T27</f>
         <v/>
       </c>
       <c r="U29" s="74">
-        <f>IFERROR(U10+U27,0)</f>
+        <f>U10+U27</f>
         <v/>
       </c>
       <c r="V29" s="74">
-        <f>IFERROR(V10+V27,0)</f>
+        <f>V10+V27</f>
         <v/>
       </c>
       <c r="W29" s="74">
-        <f>IFERROR(W10+W27,0)</f>
+        <f>W10+W27</f>
         <v/>
       </c>
       <c r="X29" s="74">
-        <f>IFERROR(X10+X27,0)</f>
+        <f>X10+X27</f>
         <v/>
       </c>
       <c r="Y29" s="74">
-        <f>IFERROR(Y10+Y27,0)</f>
+        <f>Y10+Y27</f>
         <v/>
       </c>
       <c r="Z29" s="74">
-        <f>IFERROR(Z10+Z27,0)</f>
+        <f>Z10+Z27</f>
         <v/>
       </c>
       <c r="AA29" s="74">
-        <f>IFERROR(AA10+AA27,0)</f>
+        <f>AA10+AA27</f>
         <v/>
       </c>
       <c r="AB29" s="74">
-        <f>IFERROR(AB10+AB27,0)</f>
+        <f>AB10+AB27</f>
         <v/>
       </c>
       <c r="AC29" s="74">
-        <f>IFERROR(AC10+AC27,0)</f>
+        <f>AC10+AC27</f>
         <v/>
       </c>
       <c r="AD29" s="74">
-        <f>IFERROR(AD10+AD27,0)</f>
+        <f>AD10+AD27</f>
         <v/>
       </c>
       <c r="AE29" s="74">
-        <f>IFERROR(AE10+AE27,0)</f>
+        <f>AE10+AE27</f>
         <v/>
       </c>
       <c r="AF29" s="74">
-        <f>IFERROR(AF10+AF27,0)</f>
+        <f>AF10+AF27</f>
         <v/>
       </c>
       <c r="AG29" s="74">
-        <f>IFERROR(AG10+AG27,0)</f>
+        <f>AG10+AG27</f>
         <v/>
       </c>
       <c r="AH29" s="74">
-        <f>IFERROR(AH10+AH27,0)</f>
+        <f>AH10+AH27</f>
         <v/>
       </c>
       <c r="AI29" s="74">
-        <f>IFERROR(AI10+AI27,0)</f>
+        <f>AI10+AI27</f>
         <v/>
       </c>
       <c r="AJ29" s="74">
-        <f>IFERROR(AJ10+AJ27,0)</f>
+        <f>AJ10+AJ27</f>
         <v/>
       </c>
       <c r="AK29" s="74">
-        <f>IFERROR(AK10+AK27,0)</f>
+        <f>AK10+AK27</f>
         <v/>
       </c>
       <c r="AL29" s="74">
-        <f>IFERROR(AL10+AL27,0)</f>
+        <f>AL10+AL27</f>
         <v/>
       </c>
       <c r="AM29" s="74">
-        <f>IFERROR(AM10+AM27,0)</f>
+        <f>AM10+AM27</f>
         <v/>
       </c>
       <c r="AN29" s="74">
-        <f>IFERROR(AN10+AN27,0)</f>
+        <f>AN10+AN27</f>
         <v/>
       </c>
       <c r="AO29" s="74">
-        <f>IFERROR(AO10+AO27,0)</f>
+        <f>AO10+AO27</f>
         <v/>
       </c>
       <c r="AP29" s="74">
-        <f>IFERROR(AP10+AP27,0)</f>
+        <f>AP10+AP27</f>
         <v/>
       </c>
       <c r="AQ29" s="74">
-        <f>IFERROR(AQ10+AQ27,0)</f>
+        <f>AQ10+AQ27</f>
         <v/>
       </c>
       <c r="AR29" s="74">
-        <f>IFERROR(AR10+AR27,0)</f>
+        <f>AR10+AR27</f>
         <v/>
       </c>
       <c r="AS29" s="74">
-        <f>IFERROR(AS10+AS27,0)</f>
+        <f>AS10+AS27</f>
         <v/>
       </c>
       <c r="AT29" s="74">
-        <f>IFERROR(AT10+AT27,0)</f>
+        <f>AT10+AT27</f>
         <v/>
       </c>
       <c r="AU29" s="74">
-        <f>IFERROR(AU10+AU27,0)</f>
+        <f>AU10+AU27</f>
         <v/>
       </c>
       <c r="AV29" s="74">
-        <f>IFERROR(AV10+AV27,0)</f>
+        <f>AV10+AV27</f>
         <v/>
       </c>
       <c r="AW29" s="74">
-        <f>IFERROR(AW10+AW27,0)</f>
+        <f>AW10+AW27</f>
         <v/>
       </c>
       <c r="AX29" s="74">
-        <f>IFERROR(AX10+AX27,0)</f>
+        <f>AX10+AX27</f>
         <v/>
       </c>
       <c r="AY29" s="74">
-        <f>IFERROR(AY10+AY27,0)</f>
+        <f>AY10+AY27</f>
         <v/>
       </c>
       <c r="AZ29" s="74">
-        <f>IFERROR(AZ10+AZ27,0)</f>
+        <f>AZ10+AZ27</f>
         <v/>
       </c>
       <c r="BA29" s="74">
-        <f>IFERROR(BA10+BA27,0)</f>
+        <f>BA10+BA27</f>
         <v/>
       </c>
       <c r="BB29" s="74">
-        <f>IFERROR(BB10+BB27,0)</f>
+        <f>BB10+BB27</f>
         <v/>
       </c>
       <c r="BC29" s="74">
-        <f>IFERROR(BC10+BC27,0)</f>
+        <f>BC10+BC27</f>
         <v/>
       </c>
       <c r="BD29" s="74">
-        <f>IFERROR(BD10+BD27,0)</f>
+        <f>BD10+BD27</f>
         <v/>
       </c>
       <c r="BE29" s="74">
-        <f>IFERROR(BE10+BE27,0)</f>
+        <f>BE10+BE27</f>
         <v/>
       </c>
       <c r="BF29" s="74">
-        <f>IFERROR(BF10+BF27,0)</f>
+        <f>BF10+BF27</f>
         <v/>
       </c>
       <c r="BG29" s="74">
-        <f>IFERROR(BG10+BG27,0)</f>
+        <f>BG10+BG27</f>
         <v/>
       </c>
       <c r="BH29" s="74">
-        <f>IFERROR(BH10+BH27,0)</f>
+        <f>BH10+BH27</f>
         <v/>
       </c>
       <c r="BI29" s="74">
-        <f>IFERROR(BI10+BI27,0)</f>
+        <f>BI10+BI27</f>
         <v/>
       </c>
       <c r="BJ29" s="74">
-        <f>IFERROR(BJ10+BJ27,0)</f>
+        <f>BJ10+BJ27</f>
         <v/>
       </c>
       <c r="BK29" s="74">
-        <f>IFERROR(BK10+BK27,0)</f>
+        <f>BK10+BK27</f>
         <v/>
       </c>
     </row>
@@ -13993,243 +13844,243 @@
       <c r="B31" s="52" t="n"/>
       <c r="C31" s="53" t="n"/>
       <c r="D31" s="70">
-        <f>IFERROR(D15,0)</f>
+        <f>D15</f>
         <v/>
       </c>
       <c r="E31" s="70">
-        <f>IFERROR(D31+E15,0)</f>
+        <f>D31+E15</f>
         <v/>
       </c>
       <c r="F31" s="70">
-        <f>IFERROR(E31+F15,0)</f>
+        <f>E31+F15</f>
         <v/>
       </c>
       <c r="G31" s="70">
-        <f>IFERROR(F31+G15,0)</f>
+        <f>F31+G15</f>
         <v/>
       </c>
       <c r="H31" s="70">
-        <f>IFERROR(G31+H15,0)</f>
+        <f>G31+H15</f>
         <v/>
       </c>
       <c r="I31" s="71">
-        <f>IFERROR(H31+I15,0)</f>
+        <f>H31+I15</f>
         <v/>
       </c>
       <c r="J31" s="72">
-        <f>IFERROR(I31+J15,0)</f>
+        <f>I31+J15</f>
         <v/>
       </c>
       <c r="K31" s="70">
-        <f>IFERROR(J31+K15,0)</f>
+        <f>J31+K15</f>
         <v/>
       </c>
       <c r="L31" s="70">
-        <f>IFERROR(K31+L15,0)</f>
+        <f>K31+L15</f>
         <v/>
       </c>
       <c r="M31" s="70">
-        <f>IFERROR(L31+M15,0)</f>
+        <f>L31+M15</f>
         <v/>
       </c>
       <c r="N31" s="70">
-        <f>IFERROR(M31+N15,0)</f>
+        <f>M31+N15</f>
         <v/>
       </c>
       <c r="O31" s="70">
-        <f>IFERROR(N31+O15,0)</f>
+        <f>N31+O15</f>
         <v/>
       </c>
       <c r="P31" s="71">
-        <f>IFERROR(O31+P15,0)</f>
+        <f>O31+P15</f>
         <v/>
       </c>
       <c r="Q31" s="72">
-        <f>IFERROR(P31+Q15,0)</f>
+        <f>P31+Q15</f>
         <v/>
       </c>
       <c r="R31" s="70">
-        <f>IFERROR(Q31+R15,0)</f>
+        <f>Q31+R15</f>
         <v/>
       </c>
       <c r="S31" s="70">
-        <f>IFERROR(R31+S15,0)</f>
+        <f>R31+S15</f>
         <v/>
       </c>
       <c r="T31" s="70">
-        <f>IFERROR(S31+T15,0)</f>
+        <f>S31+T15</f>
         <v/>
       </c>
       <c r="U31" s="70">
-        <f>IFERROR(T31+U15,0)</f>
+        <f>T31+U15</f>
         <v/>
       </c>
       <c r="V31" s="70">
-        <f>IFERROR(U31+V15,0)</f>
+        <f>U31+V15</f>
         <v/>
       </c>
       <c r="W31" s="71">
-        <f>IFERROR(V31+W15,0)</f>
+        <f>V31+W15</f>
         <v/>
       </c>
       <c r="X31" s="72">
-        <f>IFERROR(W31+X15,0)</f>
+        <f>W31+X15</f>
         <v/>
       </c>
       <c r="Y31" s="70">
-        <f>IFERROR(X31+Y15,0)</f>
+        <f>X31+Y15</f>
         <v/>
       </c>
       <c r="Z31" s="70">
-        <f>IFERROR(Y31+Z15,0)</f>
+        <f>Y31+Z15</f>
         <v/>
       </c>
       <c r="AA31" s="70">
-        <f>IFERROR(Z31+AA15,0)</f>
+        <f>Z31+AA15</f>
         <v/>
       </c>
       <c r="AB31" s="70">
-        <f>IFERROR(AA31+AB15,0)</f>
+        <f>AA31+AB15</f>
         <v/>
       </c>
       <c r="AC31" s="70">
-        <f>IFERROR(AB31+AC15,0)</f>
+        <f>AB31+AC15</f>
         <v/>
       </c>
       <c r="AD31" s="71">
-        <f>IFERROR(AC31+AD15,0)</f>
+        <f>AC31+AD15</f>
         <v/>
       </c>
       <c r="AE31" s="72">
-        <f>IFERROR(AD31+AE15,0)</f>
+        <f>AD31+AE15</f>
         <v/>
       </c>
       <c r="AF31" s="70">
-        <f>IFERROR(AE31+AF15,0)</f>
+        <f>AE31+AF15</f>
         <v/>
       </c>
       <c r="AG31" s="70">
-        <f>IFERROR(AF31+AG15,0)</f>
+        <f>AF31+AG15</f>
         <v/>
       </c>
       <c r="AH31" s="70">
-        <f>IFERROR(AG31+AH15,0)</f>
+        <f>AG31+AH15</f>
         <v/>
       </c>
       <c r="AI31" s="70">
-        <f>IFERROR(AH31+AI15,0)</f>
+        <f>AH31+AI15</f>
         <v/>
       </c>
       <c r="AJ31" s="70">
-        <f>IFERROR(AI31+AJ15,0)</f>
+        <f>AI31+AJ15</f>
         <v/>
       </c>
       <c r="AK31" s="71">
-        <f>IFERROR(AJ31+AK15,0)</f>
+        <f>AJ31+AK15</f>
         <v/>
       </c>
       <c r="AL31" s="72">
-        <f>IFERROR(AK31+AL15,0)</f>
+        <f>AK31+AL15</f>
         <v/>
       </c>
       <c r="AM31" s="70">
-        <f>IFERROR(AL31+AM15,0)</f>
+        <f>AL31+AM15</f>
         <v/>
       </c>
       <c r="AN31" s="70">
-        <f>IFERROR(AM31+AN15,0)</f>
+        <f>AM31+AN15</f>
         <v/>
       </c>
       <c r="AO31" s="70">
-        <f>IFERROR(AN31+AO15,0)</f>
+        <f>AN31+AO15</f>
         <v/>
       </c>
       <c r="AP31" s="70">
-        <f>IFERROR(AO31+AP15,0)</f>
+        <f>AO31+AP15</f>
         <v/>
       </c>
       <c r="AQ31" s="70">
-        <f>IFERROR(AP31+AQ15,0)</f>
+        <f>AP31+AQ15</f>
         <v/>
       </c>
       <c r="AR31" s="71">
-        <f>IFERROR(AQ31+AR15,0)</f>
+        <f>AQ31+AR15</f>
         <v/>
       </c>
       <c r="AS31" s="72">
-        <f>IFERROR(AR31+AS15,0)</f>
+        <f>AR31+AS15</f>
         <v/>
       </c>
       <c r="AT31" s="70">
-        <f>IFERROR(AS31+AT15,0)</f>
+        <f>AS31+AT15</f>
         <v/>
       </c>
       <c r="AU31" s="70">
-        <f>IFERROR(AT31+AU15,0)</f>
+        <f>AT31+AU15</f>
         <v/>
       </c>
       <c r="AV31" s="70">
-        <f>IFERROR(AU31+AV15,0)</f>
+        <f>AU31+AV15</f>
         <v/>
       </c>
       <c r="AW31" s="70">
-        <f>IFERROR(AV31+AW15,0)</f>
+        <f>AV31+AW15</f>
         <v/>
       </c>
       <c r="AX31" s="70">
-        <f>IFERROR(AW31+AX15,0)</f>
+        <f>AW31+AX15</f>
         <v/>
       </c>
       <c r="AY31" s="71">
-        <f>IFERROR(AX31+AY15,0)</f>
+        <f>AX31+AY15</f>
         <v/>
       </c>
       <c r="AZ31" s="72">
-        <f>IFERROR(AY31+AZ15,0)</f>
+        <f>AY31+AZ15</f>
         <v/>
       </c>
       <c r="BA31" s="70">
-        <f>IFERROR(AZ31+BA15,0)</f>
+        <f>AZ31+BA15</f>
         <v/>
       </c>
       <c r="BB31" s="70">
-        <f>IFERROR(BA31+BB15,0)</f>
+        <f>BA31+BB15</f>
         <v/>
       </c>
       <c r="BC31" s="70">
-        <f>IFERROR(BB31+BC15,0)</f>
+        <f>BB31+BC15</f>
         <v/>
       </c>
       <c r="BD31" s="70">
-        <f>IFERROR(BC31+BD15,0)</f>
+        <f>BC31+BD15</f>
         <v/>
       </c>
       <c r="BE31" s="70">
-        <f>IFERROR(BD31+BE15,0)</f>
+        <f>BD31+BE15</f>
         <v/>
       </c>
       <c r="BF31" s="71">
-        <f>IFERROR(BE31+BF15,0)</f>
+        <f>BE31+BF15</f>
         <v/>
       </c>
       <c r="BG31" s="72">
-        <f>IFERROR(BF31+BG15,0)</f>
+        <f>BF31+BG15</f>
         <v/>
       </c>
       <c r="BH31" s="70">
-        <f>IFERROR(BG31+BH15,0)</f>
+        <f>BG31+BH15</f>
         <v/>
       </c>
       <c r="BI31" s="70">
-        <f>IFERROR(BH31+BI15,0)</f>
+        <f>BH31+BI15</f>
         <v/>
       </c>
       <c r="BJ31" s="70">
-        <f>IFERROR(BI31+BJ15,0)</f>
+        <f>BI31+BJ15</f>
         <v/>
       </c>
       <c r="BK31" s="70">
-        <f>IFERROR(BJ31+BK15,0)</f>
+        <f>BJ31+BK15</f>
         <v/>
       </c>
     </row>
@@ -14242,243 +14093,243 @@
       <c r="B32" s="52" t="n"/>
       <c r="C32" s="53" t="n"/>
       <c r="D32" s="70">
-        <f>IFERROR(D25,0)</f>
+        <f>D25</f>
         <v/>
       </c>
       <c r="E32" s="70">
-        <f>IFERROR(D32+E25,0)</f>
+        <f>D32+E25</f>
         <v/>
       </c>
       <c r="F32" s="70">
-        <f>IFERROR(E32+F25,0)</f>
+        <f>E32+F25</f>
         <v/>
       </c>
       <c r="G32" s="70">
-        <f>IFERROR(F32+G25,0)</f>
+        <f>F32+G25</f>
         <v/>
       </c>
       <c r="H32" s="70">
-        <f>IFERROR(G32+H25,0)</f>
+        <f>G32+H25</f>
         <v/>
       </c>
       <c r="I32" s="71">
-        <f>IFERROR(H32+I25,0)</f>
+        <f>H32+I25</f>
         <v/>
       </c>
       <c r="J32" s="72">
-        <f>IFERROR(I32+J25,0)</f>
+        <f>I32+J25</f>
         <v/>
       </c>
       <c r="K32" s="70">
-        <f>IFERROR(J32+K25,0)</f>
+        <f>J32+K25</f>
         <v/>
       </c>
       <c r="L32" s="70">
-        <f>IFERROR(K32+L25,0)</f>
+        <f>K32+L25</f>
         <v/>
       </c>
       <c r="M32" s="70">
-        <f>IFERROR(L32+M25,0)</f>
+        <f>L32+M25</f>
         <v/>
       </c>
       <c r="N32" s="70">
-        <f>IFERROR(M32+N25,0)</f>
+        <f>M32+N25</f>
         <v/>
       </c>
       <c r="O32" s="70">
-        <f>IFERROR(N32+O25,0)</f>
+        <f>N32+O25</f>
         <v/>
       </c>
       <c r="P32" s="71">
-        <f>IFERROR(O32+P25,0)</f>
+        <f>O32+P25</f>
         <v/>
       </c>
       <c r="Q32" s="72">
-        <f>IFERROR(P32+Q25,0)</f>
+        <f>P32+Q25</f>
         <v/>
       </c>
       <c r="R32" s="70">
-        <f>IFERROR(Q32+R25,0)</f>
+        <f>Q32+R25</f>
         <v/>
       </c>
       <c r="S32" s="70">
-        <f>IFERROR(R32+S25,0)</f>
+        <f>R32+S25</f>
         <v/>
       </c>
       <c r="T32" s="70">
-        <f>IFERROR(S32+T25,0)</f>
+        <f>S32+T25</f>
         <v/>
       </c>
       <c r="U32" s="70">
-        <f>IFERROR(T32+U25,0)</f>
+        <f>T32+U25</f>
         <v/>
       </c>
       <c r="V32" s="70">
-        <f>IFERROR(U32+V25,0)</f>
+        <f>U32+V25</f>
         <v/>
       </c>
       <c r="W32" s="71">
-        <f>IFERROR(V32+W25,0)</f>
+        <f>V32+W25</f>
         <v/>
       </c>
       <c r="X32" s="72">
-        <f>IFERROR(W32+X25,0)</f>
+        <f>W32+X25</f>
         <v/>
       </c>
       <c r="Y32" s="70">
-        <f>IFERROR(X32+Y25,0)</f>
+        <f>X32+Y25</f>
         <v/>
       </c>
       <c r="Z32" s="70">
-        <f>IFERROR(Y32+Z25,0)</f>
+        <f>Y32+Z25</f>
         <v/>
       </c>
       <c r="AA32" s="70">
-        <f>IFERROR(Z32+AA25,0)</f>
+        <f>Z32+AA25</f>
         <v/>
       </c>
       <c r="AB32" s="70">
-        <f>IFERROR(AA32+AB25,0)</f>
+        <f>AA32+AB25</f>
         <v/>
       </c>
       <c r="AC32" s="70">
-        <f>IFERROR(AB32+AC25,0)</f>
+        <f>AB32+AC25</f>
         <v/>
       </c>
       <c r="AD32" s="71">
-        <f>IFERROR(AC32+AD25,0)</f>
+        <f>AC32+AD25</f>
         <v/>
       </c>
       <c r="AE32" s="72">
-        <f>IFERROR(AD32+AE25,0)</f>
+        <f>AD32+AE25</f>
         <v/>
       </c>
       <c r="AF32" s="70">
-        <f>IFERROR(AE32+AF25,0)</f>
+        <f>AE32+AF25</f>
         <v/>
       </c>
       <c r="AG32" s="70">
-        <f>IFERROR(AF32+AG25,0)</f>
+        <f>AF32+AG25</f>
         <v/>
       </c>
       <c r="AH32" s="70">
-        <f>IFERROR(AG32+AH25,0)</f>
+        <f>AG32+AH25</f>
         <v/>
       </c>
       <c r="AI32" s="70">
-        <f>IFERROR(AH32+AI25,0)</f>
+        <f>AH32+AI25</f>
         <v/>
       </c>
       <c r="AJ32" s="70">
-        <f>IFERROR(AI32+AJ25,0)</f>
+        <f>AI32+AJ25</f>
         <v/>
       </c>
       <c r="AK32" s="71">
-        <f>IFERROR(AJ32+AK25,0)</f>
+        <f>AJ32+AK25</f>
         <v/>
       </c>
       <c r="AL32" s="72">
-        <f>IFERROR(AK32+AL25,0)</f>
+        <f>AK32+AL25</f>
         <v/>
       </c>
       <c r="AM32" s="70">
-        <f>IFERROR(AL32+AM25,0)</f>
+        <f>AL32+AM25</f>
         <v/>
       </c>
       <c r="AN32" s="70">
-        <f>IFERROR(AM32+AN25,0)</f>
+        <f>AM32+AN25</f>
         <v/>
       </c>
       <c r="AO32" s="70">
-        <f>IFERROR(AN32+AO25,0)</f>
+        <f>AN32+AO25</f>
         <v/>
       </c>
       <c r="AP32" s="70">
-        <f>IFERROR(AO32+AP25,0)</f>
+        <f>AO32+AP25</f>
         <v/>
       </c>
       <c r="AQ32" s="70">
-        <f>IFERROR(AP32+AQ25,0)</f>
+        <f>AP32+AQ25</f>
         <v/>
       </c>
       <c r="AR32" s="71">
-        <f>IFERROR(AQ32+AR25,0)</f>
+        <f>AQ32+AR25</f>
         <v/>
       </c>
       <c r="AS32" s="72">
-        <f>IFERROR(AR32+AS25,0)</f>
+        <f>AR32+AS25</f>
         <v/>
       </c>
       <c r="AT32" s="70">
-        <f>IFERROR(AS32+AT25,0)</f>
+        <f>AS32+AT25</f>
         <v/>
       </c>
       <c r="AU32" s="70">
-        <f>IFERROR(AT32+AU25,0)</f>
+        <f>AT32+AU25</f>
         <v/>
       </c>
       <c r="AV32" s="70">
-        <f>IFERROR(AU32+AV25,0)</f>
+        <f>AU32+AV25</f>
         <v/>
       </c>
       <c r="AW32" s="70">
-        <f>IFERROR(AV32+AW25,0)</f>
+        <f>AV32+AW25</f>
         <v/>
       </c>
       <c r="AX32" s="70">
-        <f>IFERROR(AW32+AX25,0)</f>
+        <f>AW32+AX25</f>
         <v/>
       </c>
       <c r="AY32" s="71">
-        <f>IFERROR(AX32+AY25,0)</f>
+        <f>AX32+AY25</f>
         <v/>
       </c>
       <c r="AZ32" s="72">
-        <f>IFERROR(AY32+AZ25,0)</f>
+        <f>AY32+AZ25</f>
         <v/>
       </c>
       <c r="BA32" s="70">
-        <f>IFERROR(AZ32+BA25,0)</f>
+        <f>AZ32+BA25</f>
         <v/>
       </c>
       <c r="BB32" s="70">
-        <f>IFERROR(BA32+BB25,0)</f>
+        <f>BA32+BB25</f>
         <v/>
       </c>
       <c r="BC32" s="70">
-        <f>IFERROR(BB32+BC25,0)</f>
+        <f>BB32+BC25</f>
         <v/>
       </c>
       <c r="BD32" s="70">
-        <f>IFERROR(BC32+BD25,0)</f>
+        <f>BC32+BD25</f>
         <v/>
       </c>
       <c r="BE32" s="70">
-        <f>IFERROR(BD32+BE25,0)</f>
+        <f>BD32+BE25</f>
         <v/>
       </c>
       <c r="BF32" s="71">
-        <f>IFERROR(BE32+BF25,0)</f>
+        <f>BE32+BF25</f>
         <v/>
       </c>
       <c r="BG32" s="72">
-        <f>IFERROR(BF32+BG25,0)</f>
+        <f>BF32+BG25</f>
         <v/>
       </c>
       <c r="BH32" s="70">
-        <f>IFERROR(BG32+BH25,0)</f>
+        <f>BG32+BH25</f>
         <v/>
       </c>
       <c r="BI32" s="70">
-        <f>IFERROR(BH32+BI25,0)</f>
+        <f>BH32+BI25</f>
         <v/>
       </c>
       <c r="BJ32" s="70">
-        <f>IFERROR(BI32+BJ25,0)</f>
+        <f>BI32+BJ25</f>
         <v/>
       </c>
       <c r="BK32" s="70">
-        <f>IFERROR(BJ32+BK25,0)</f>
+        <f>BJ32+BK25</f>
         <v/>
       </c>
     </row>
@@ -14491,243 +14342,243 @@
       <c r="B33" s="52" t="n"/>
       <c r="C33" s="53" t="n"/>
       <c r="D33" s="75">
-        <f>IFERROR(D29,0)</f>
+        <f>D29</f>
         <v/>
       </c>
       <c r="E33" s="75">
-        <f>IFERROR(E29,0)</f>
+        <f>E29</f>
         <v/>
       </c>
       <c r="F33" s="75">
-        <f>IFERROR(F29,0)</f>
+        <f>F29</f>
         <v/>
       </c>
       <c r="G33" s="75">
-        <f>IFERROR(G29,0)</f>
+        <f>G29</f>
         <v/>
       </c>
       <c r="H33" s="75">
-        <f>IFERROR(H29,0)</f>
+        <f>H29</f>
         <v/>
       </c>
       <c r="I33" s="75">
-        <f>IFERROR(I29,0)</f>
+        <f>I29</f>
         <v/>
       </c>
       <c r="J33" s="75">
-        <f>IFERROR(J29,0)</f>
+        <f>J29</f>
         <v/>
       </c>
       <c r="K33" s="75">
-        <f>IFERROR(K29,0)</f>
+        <f>K29</f>
         <v/>
       </c>
       <c r="L33" s="75">
-        <f>IFERROR(L29,0)</f>
+        <f>L29</f>
         <v/>
       </c>
       <c r="M33" s="75">
-        <f>IFERROR(M29,0)</f>
+        <f>M29</f>
         <v/>
       </c>
       <c r="N33" s="75">
-        <f>IFERROR(N29,0)</f>
+        <f>N29</f>
         <v/>
       </c>
       <c r="O33" s="75">
-        <f>IFERROR(O29,0)</f>
+        <f>O29</f>
         <v/>
       </c>
       <c r="P33" s="75">
-        <f>IFERROR(P29,0)</f>
+        <f>P29</f>
         <v/>
       </c>
       <c r="Q33" s="75">
-        <f>IFERROR(Q29,0)</f>
+        <f>Q29</f>
         <v/>
       </c>
       <c r="R33" s="75">
-        <f>IFERROR(R29,0)</f>
+        <f>R29</f>
         <v/>
       </c>
       <c r="S33" s="75">
-        <f>IFERROR(S29,0)</f>
+        <f>S29</f>
         <v/>
       </c>
       <c r="T33" s="75">
-        <f>IFERROR(T29,0)</f>
+        <f>T29</f>
         <v/>
       </c>
       <c r="U33" s="75">
-        <f>IFERROR(U29,0)</f>
+        <f>U29</f>
         <v/>
       </c>
       <c r="V33" s="75">
-        <f>IFERROR(V29,0)</f>
+        <f>V29</f>
         <v/>
       </c>
       <c r="W33" s="75">
-        <f>IFERROR(W29,0)</f>
+        <f>W29</f>
         <v/>
       </c>
       <c r="X33" s="75">
-        <f>IFERROR(X29,0)</f>
+        <f>X29</f>
         <v/>
       </c>
       <c r="Y33" s="75">
-        <f>IFERROR(Y29,0)</f>
+        <f>Y29</f>
         <v/>
       </c>
       <c r="Z33" s="75">
-        <f>IFERROR(Z29,0)</f>
+        <f>Z29</f>
         <v/>
       </c>
       <c r="AA33" s="75">
-        <f>IFERROR(AA29,0)</f>
+        <f>AA29</f>
         <v/>
       </c>
       <c r="AB33" s="75">
-        <f>IFERROR(AB29,0)</f>
+        <f>AB29</f>
         <v/>
       </c>
       <c r="AC33" s="75">
-        <f>IFERROR(AC29,0)</f>
+        <f>AC29</f>
         <v/>
       </c>
       <c r="AD33" s="75">
-        <f>IFERROR(AD29,0)</f>
+        <f>AD29</f>
         <v/>
       </c>
       <c r="AE33" s="75">
-        <f>IFERROR(AE29,0)</f>
+        <f>AE29</f>
         <v/>
       </c>
       <c r="AF33" s="75">
-        <f>IFERROR(AF29,0)</f>
+        <f>AF29</f>
         <v/>
       </c>
       <c r="AG33" s="75">
-        <f>IFERROR(AG29,0)</f>
+        <f>AG29</f>
         <v/>
       </c>
       <c r="AH33" s="75">
-        <f>IFERROR(AH29,0)</f>
+        <f>AH29</f>
         <v/>
       </c>
       <c r="AI33" s="75">
-        <f>IFERROR(AI29,0)</f>
+        <f>AI29</f>
         <v/>
       </c>
       <c r="AJ33" s="75">
-        <f>IFERROR(AJ29,0)</f>
+        <f>AJ29</f>
         <v/>
       </c>
       <c r="AK33" s="75">
-        <f>IFERROR(AK29,0)</f>
+        <f>AK29</f>
         <v/>
       </c>
       <c r="AL33" s="75">
-        <f>IFERROR(AL29,0)</f>
+        <f>AL29</f>
         <v/>
       </c>
       <c r="AM33" s="75">
-        <f>IFERROR(AM29,0)</f>
+        <f>AM29</f>
         <v/>
       </c>
       <c r="AN33" s="75">
-        <f>IFERROR(AN29,0)</f>
+        <f>AN29</f>
         <v/>
       </c>
       <c r="AO33" s="75">
-        <f>IFERROR(AO29,0)</f>
+        <f>AO29</f>
         <v/>
       </c>
       <c r="AP33" s="75">
-        <f>IFERROR(AP29,0)</f>
+        <f>AP29</f>
         <v/>
       </c>
       <c r="AQ33" s="75">
-        <f>IFERROR(AQ29,0)</f>
+        <f>AQ29</f>
         <v/>
       </c>
       <c r="AR33" s="75">
-        <f>IFERROR(AR29,0)</f>
+        <f>AR29</f>
         <v/>
       </c>
       <c r="AS33" s="75">
-        <f>IFERROR(AS29,0)</f>
+        <f>AS29</f>
         <v/>
       </c>
       <c r="AT33" s="75">
-        <f>IFERROR(AT29,0)</f>
+        <f>AT29</f>
         <v/>
       </c>
       <c r="AU33" s="75">
-        <f>IFERROR(AU29,0)</f>
+        <f>AU29</f>
         <v/>
       </c>
       <c r="AV33" s="75">
-        <f>IFERROR(AV29,0)</f>
+        <f>AV29</f>
         <v/>
       </c>
       <c r="AW33" s="75">
-        <f>IFERROR(AW29,0)</f>
+        <f>AW29</f>
         <v/>
       </c>
       <c r="AX33" s="75">
-        <f>IFERROR(AX29,0)</f>
+        <f>AX29</f>
         <v/>
       </c>
       <c r="AY33" s="75">
-        <f>IFERROR(AY29,0)</f>
+        <f>AY29</f>
         <v/>
       </c>
       <c r="AZ33" s="75">
-        <f>IFERROR(AZ29,0)</f>
+        <f>AZ29</f>
         <v/>
       </c>
       <c r="BA33" s="75">
-        <f>IFERROR(BA29,0)</f>
+        <f>BA29</f>
         <v/>
       </c>
       <c r="BB33" s="75">
-        <f>IFERROR(BB29,0)</f>
+        <f>BB29</f>
         <v/>
       </c>
       <c r="BC33" s="75">
-        <f>IFERROR(BC29,0)</f>
+        <f>BC29</f>
         <v/>
       </c>
       <c r="BD33" s="75">
-        <f>IFERROR(BD29,0)</f>
+        <f>BD29</f>
         <v/>
       </c>
       <c r="BE33" s="75">
-        <f>IFERROR(BE29,0)</f>
+        <f>BE29</f>
         <v/>
       </c>
       <c r="BF33" s="75">
-        <f>IFERROR(BF29,0)</f>
+        <f>BF29</f>
         <v/>
       </c>
       <c r="BG33" s="75">
-        <f>IFERROR(BG29,0)</f>
+        <f>BG29</f>
         <v/>
       </c>
       <c r="BH33" s="75">
-        <f>IFERROR(BH29,0)</f>
+        <f>BH29</f>
         <v/>
       </c>
       <c r="BI33" s="75">
-        <f>IFERROR(BI29,0)</f>
+        <f>BI29</f>
         <v/>
       </c>
       <c r="BJ33" s="75">
-        <f>IFERROR(BJ29,0)</f>
+        <f>BJ29</f>
         <v/>
       </c>
       <c r="BK33" s="75">
-        <f>IFERROR(BK29,0)</f>
+        <f>BK29</f>
         <v/>
       </c>
     </row>
@@ -15570,184 +15421,184 @@
       <c r="B6" s="78" t="n"/>
       <c r="C6" s="78" t="n"/>
       <c r="D6" s="78" t="n"/>
-      <c r="E6" s="97" t="n">
+      <c r="E6" s="101" t="n">
         <v>45627</v>
       </c>
-      <c r="F6" s="97" t="n">
+      <c r="F6" s="101" t="n">
         <v>45628</v>
       </c>
-      <c r="G6" s="97" t="n">
+      <c r="G6" s="101" t="n">
         <v>45629</v>
       </c>
-      <c r="H6" s="97" t="n">
+      <c r="H6" s="101" t="n">
         <v>45630</v>
       </c>
-      <c r="I6" s="97" t="n">
+      <c r="I6" s="101" t="n">
         <v>45631</v>
       </c>
-      <c r="J6" s="98" t="n">
+      <c r="J6" s="102" t="n">
         <v>45632</v>
       </c>
-      <c r="K6" s="99" t="n">
+      <c r="K6" s="103" t="n">
         <v>45633</v>
       </c>
-      <c r="L6" s="97" t="n">
+      <c r="L6" s="101" t="n">
         <v>45634</v>
       </c>
-      <c r="M6" s="97" t="n">
+      <c r="M6" s="101" t="n">
         <v>45635</v>
       </c>
-      <c r="N6" s="97" t="n">
+      <c r="N6" s="101" t="n">
         <v>45636</v>
       </c>
-      <c r="O6" s="97" t="n">
+      <c r="O6" s="101" t="n">
         <v>45637</v>
       </c>
-      <c r="P6" s="97" t="n">
+      <c r="P6" s="101" t="n">
         <v>45638</v>
       </c>
-      <c r="Q6" s="98" t="n">
+      <c r="Q6" s="102" t="n">
         <v>45639</v>
       </c>
-      <c r="R6" s="99" t="n">
+      <c r="R6" s="103" t="n">
         <v>45640</v>
       </c>
-      <c r="S6" s="97" t="n">
+      <c r="S6" s="101" t="n">
         <v>45641</v>
       </c>
-      <c r="T6" s="97" t="n">
+      <c r="T6" s="101" t="n">
         <v>45642</v>
       </c>
-      <c r="U6" s="97" t="n">
+      <c r="U6" s="101" t="n">
         <v>45643</v>
       </c>
-      <c r="V6" s="97" t="n">
+      <c r="V6" s="101" t="n">
         <v>45644</v>
       </c>
-      <c r="W6" s="97" t="n">
+      <c r="W6" s="101" t="n">
         <v>45645</v>
       </c>
-      <c r="X6" s="98" t="n">
+      <c r="X6" s="102" t="n">
         <v>45646</v>
       </c>
-      <c r="Y6" s="99" t="n">
+      <c r="Y6" s="103" t="n">
         <v>45647</v>
       </c>
-      <c r="Z6" s="97" t="n">
+      <c r="Z6" s="101" t="n">
         <v>45648</v>
       </c>
-      <c r="AA6" s="97" t="n">
+      <c r="AA6" s="101" t="n">
         <v>45649</v>
       </c>
-      <c r="AB6" s="97" t="n">
+      <c r="AB6" s="101" t="n">
         <v>45650</v>
       </c>
-      <c r="AC6" s="97" t="n">
+      <c r="AC6" s="101" t="n">
         <v>45651</v>
       </c>
-      <c r="AD6" s="97" t="n">
+      <c r="AD6" s="101" t="n">
         <v>45652</v>
       </c>
-      <c r="AE6" s="98" t="n">
+      <c r="AE6" s="102" t="n">
         <v>45653</v>
       </c>
-      <c r="AF6" s="99" t="n">
+      <c r="AF6" s="103" t="n">
         <v>45654</v>
       </c>
-      <c r="AG6" s="97" t="n">
+      <c r="AG6" s="101" t="n">
         <v>45655</v>
       </c>
-      <c r="AH6" s="97" t="n">
+      <c r="AH6" s="101" t="n">
         <v>45656</v>
       </c>
-      <c r="AI6" s="97" t="n">
+      <c r="AI6" s="101" t="n">
         <v>45657</v>
       </c>
-      <c r="AJ6" s="97" t="n">
+      <c r="AJ6" s="101" t="n">
         <v>45658</v>
       </c>
-      <c r="AK6" s="97" t="n">
+      <c r="AK6" s="101" t="n">
         <v>45659</v>
       </c>
-      <c r="AL6" s="98" t="n">
+      <c r="AL6" s="102" t="n">
         <v>45660</v>
       </c>
-      <c r="AM6" s="99" t="n">
+      <c r="AM6" s="103" t="n">
         <v>45661</v>
       </c>
-      <c r="AN6" s="97" t="n">
+      <c r="AN6" s="101" t="n">
         <v>45662</v>
       </c>
-      <c r="AO6" s="97" t="n">
+      <c r="AO6" s="101" t="n">
         <v>45663</v>
       </c>
-      <c r="AP6" s="97" t="n">
+      <c r="AP6" s="101" t="n">
         <v>45664</v>
       </c>
-      <c r="AQ6" s="97" t="n">
+      <c r="AQ6" s="101" t="n">
         <v>45665</v>
       </c>
-      <c r="AR6" s="97" t="n">
+      <c r="AR6" s="101" t="n">
         <v>45666</v>
       </c>
-      <c r="AS6" s="98" t="n">
+      <c r="AS6" s="102" t="n">
         <v>45667</v>
       </c>
-      <c r="AT6" s="99" t="n">
+      <c r="AT6" s="103" t="n">
         <v>45668</v>
       </c>
-      <c r="AU6" s="97" t="n">
+      <c r="AU6" s="101" t="n">
         <v>45669</v>
       </c>
-      <c r="AV6" s="97" t="n">
+      <c r="AV6" s="101" t="n">
         <v>45670</v>
       </c>
-      <c r="AW6" s="97" t="n">
+      <c r="AW6" s="101" t="n">
         <v>45671</v>
       </c>
-      <c r="AX6" s="97" t="n">
+      <c r="AX6" s="101" t="n">
         <v>45672</v>
       </c>
-      <c r="AY6" s="97" t="n">
+      <c r="AY6" s="101" t="n">
         <v>45673</v>
       </c>
-      <c r="AZ6" s="98" t="n">
+      <c r="AZ6" s="102" t="n">
         <v>45674</v>
       </c>
-      <c r="BA6" s="99" t="n">
+      <c r="BA6" s="103" t="n">
         <v>45675</v>
       </c>
-      <c r="BB6" s="97" t="n">
+      <c r="BB6" s="101" t="n">
         <v>45676</v>
       </c>
-      <c r="BC6" s="97" t="n">
+      <c r="BC6" s="101" t="n">
         <v>45677</v>
       </c>
-      <c r="BD6" s="97" t="n">
+      <c r="BD6" s="101" t="n">
         <v>45678</v>
       </c>
-      <c r="BE6" s="97" t="n">
+      <c r="BE6" s="101" t="n">
         <v>45679</v>
       </c>
-      <c r="BF6" s="97" t="n">
+      <c r="BF6" s="101" t="n">
         <v>45680</v>
       </c>
-      <c r="BG6" s="98" t="n">
+      <c r="BG6" s="102" t="n">
         <v>45681</v>
       </c>
-      <c r="BH6" s="99" t="n">
+      <c r="BH6" s="103" t="n">
         <v>45682</v>
       </c>
-      <c r="BI6" s="97" t="n">
+      <c r="BI6" s="101" t="n">
         <v>45683</v>
       </c>
-      <c r="BJ6" s="97" t="n">
+      <c r="BJ6" s="101" t="n">
         <v>45684</v>
       </c>
-      <c r="BK6" s="97" t="n">
+      <c r="BK6" s="101" t="n">
         <v>45685</v>
       </c>
-      <c r="BL6" s="97" t="n">
+      <c r="BL6" s="101" t="n">
         <v>45686</v>
       </c>
     </row>
@@ -17854,243 +17705,243 @@
         <v/>
       </c>
       <c r="E17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=E$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=E$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="F17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=F$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=F$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="G17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=G$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=G$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="H17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=H$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=H$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="I17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=I$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=I$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="J17" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=J$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=J$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="K17" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=K$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=K$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="L17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=L$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=L$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="M17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=M$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=M$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="N17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=N$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=N$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="O17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=O$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=O$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="P17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=P$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=P$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="Q17" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=Q$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=Q$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="R17" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=R$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=R$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="S17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=S$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=S$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="T17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=T$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=T$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="U17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=U$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=U$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="V17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=V$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=V$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="W17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=W$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=W$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="X17" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=X$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=X$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="Y17" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=Y$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=Y$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="Z17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=Z$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=Z$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AA17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AA$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AA$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AB17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AB$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AB$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AC17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AC$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AC$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AD17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AD$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AD$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AE17" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AE$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AE$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AF17" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AF$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AF$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AG17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AG$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AG$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AH17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AH$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AH$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AI17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AI$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AI$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AJ17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AJ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AJ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AK17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AK$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AK$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AL17" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AL$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AL$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AM17" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AM$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AM$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AN17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AN$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AN$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AO17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AO$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AO$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AP17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AP$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AP$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AQ17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AQ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AQ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AR17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AR$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AR$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AS17" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AS$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AS$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AT17" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AT$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AT$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AU17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AU$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AU$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AV17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AV$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AV$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AW17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AW$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AW$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AX17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AX$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AX$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AY17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AY$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AY$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AZ17" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=AZ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=AZ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BA17" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BA$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BA$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BB17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BB$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BB$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BC17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BC$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BC$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BD17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BD$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BD$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BE17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BE$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BE$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BF17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BF$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BF$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BG17" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BG$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BG$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BH17" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BH$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BH$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BI17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BI$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BI$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BJ17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BJ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BJ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BK17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BK$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BK$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BL17" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="HR-002")*(Payment_Data.$J$6:$J$100=BL$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-008")*(Payment_Data.$J$6:$J$100=BL$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
     </row>
@@ -18968,243 +18819,243 @@
         <v/>
       </c>
       <c r="E22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=E$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=E$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="F22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=F$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=F$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="G22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=G$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=G$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="H22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=H$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=H$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="I22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=I$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=I$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="J22" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=J$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=J$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="K22" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=K$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=K$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="L22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=L$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=L$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="M22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=M$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=M$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="N22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=N$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=N$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="O22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=O$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=O$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="P22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=P$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=P$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="Q22" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=Q$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=Q$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="R22" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=R$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=R$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="S22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=S$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=S$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="T22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=T$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=T$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="U22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=U$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=U$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="V22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=V$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=V$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="W22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=W$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=W$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="X22" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=X$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=X$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="Y22" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=Y$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=Y$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="Z22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=Z$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=Z$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AA22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AA$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AA$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AB22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AB$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AB$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AC22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AC$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AC$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AD22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AD$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AD$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AE22" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AE$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AE$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AF22" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AF$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AF$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AG22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AG$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AG$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AH22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AH$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AH$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AI22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AI$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AI$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AJ22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AJ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AJ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AK22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AK$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AK$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AL22" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AL$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AL$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AM22" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AM$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AM$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AN22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AN$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AN$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AO22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AO$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AO$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AP22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AP$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AP$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AQ22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AQ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AQ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AR22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AR$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AR$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AS22" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AS$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AS$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AT22" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AT$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AT$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AU22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AU$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AU$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AV22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AV$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AV$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AW22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AW$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AW$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AX22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AX$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AX$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AY22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AY$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AY$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AZ22" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=AZ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=AZ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BA22" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BA$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BA$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BB22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BB$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BB$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BC22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BC$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BC$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BD22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BD$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BD$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BE22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BE$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BE$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BF22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BF$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BF$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BG22" s="71">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BG$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BG$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BH22" s="72">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BH$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BH$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BI22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BI$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BI$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BJ22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BJ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BJ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BK22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BK$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BK$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BL22" s="70">
-        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="GOV-001")*(Payment_Data.$J$6:$J$100=BL$6)*(Payment_Data.$I$6:$I$100)),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-013")*(Payment_Data.$J$6:$J$100=BL$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
     </row>
@@ -23160,243 +23011,243 @@
       </c>
       <c r="D41" s="85" t="inlineStr"/>
       <c r="E41" s="74">
-        <f>IFERROR(SUM(E10:E40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=E$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="F41" s="74">
-        <f>IFERROR(SUM(F10:F40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=F$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="G41" s="74">
-        <f>IFERROR(SUM(G10:G40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=G$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="H41" s="74">
-        <f>IFERROR(SUM(H10:H40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=H$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="I41" s="74">
-        <f>IFERROR(SUM(I10:I40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=I$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="J41" s="74">
-        <f>IFERROR(SUM(J10:J40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=J$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="K41" s="74">
-        <f>IFERROR(SUM(K10:K40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=K$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="L41" s="74">
-        <f>IFERROR(SUM(L10:L40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=L$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="M41" s="74">
-        <f>IFERROR(SUM(M10:M40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=M$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="N41" s="74">
-        <f>IFERROR(SUM(N10:N40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=N$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="O41" s="74">
-        <f>IFERROR(SUM(O10:O40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=O$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="P41" s="74">
-        <f>IFERROR(SUM(P10:P40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=P$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="Q41" s="74">
-        <f>IFERROR(SUM(Q10:Q40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=Q$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="R41" s="74">
-        <f>IFERROR(SUM(R10:R40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=R$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="S41" s="74">
-        <f>IFERROR(SUM(S10:S40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=S$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="T41" s="74">
-        <f>IFERROR(SUM(T10:T40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=T$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="U41" s="74">
-        <f>IFERROR(SUM(U10:U40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=U$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="V41" s="74">
-        <f>IFERROR(SUM(V10:V40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=V$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="W41" s="74">
-        <f>IFERROR(SUM(W10:W40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=W$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="X41" s="74">
-        <f>IFERROR(SUM(X10:X40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=X$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="Y41" s="74">
-        <f>IFERROR(SUM(Y10:Y40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=Y$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="Z41" s="74">
-        <f>IFERROR(SUM(Z10:Z40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=Z$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AA41" s="74">
-        <f>IFERROR(SUM(AA10:AA40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AA$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AB41" s="74">
-        <f>IFERROR(SUM(AB10:AB40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AB$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AC41" s="74">
-        <f>IFERROR(SUM(AC10:AC40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AC$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AD41" s="74">
-        <f>IFERROR(SUM(AD10:AD40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AD$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AE41" s="74">
-        <f>IFERROR(SUM(AE10:AE40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AE$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AF41" s="74">
-        <f>IFERROR(SUM(AF10:AF40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AF$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AG41" s="74">
-        <f>IFERROR(SUM(AG10:AG40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AG$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AH41" s="74">
-        <f>IFERROR(SUM(AH10:AH40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AH$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AI41" s="74">
-        <f>IFERROR(SUM(AI10:AI40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AI$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AJ41" s="74">
-        <f>IFERROR(SUM(AJ10:AJ40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AJ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AK41" s="74">
-        <f>IFERROR(SUM(AK10:AK40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AK$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AL41" s="74">
-        <f>IFERROR(SUM(AL10:AL40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AL$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AM41" s="74">
-        <f>IFERROR(SUM(AM10:AM40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AM$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AN41" s="74">
-        <f>IFERROR(SUM(AN10:AN40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AN$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AO41" s="74">
-        <f>IFERROR(SUM(AO10:AO40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AO$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AP41" s="74">
-        <f>IFERROR(SUM(AP10:AP40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AP$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AQ41" s="74">
-        <f>IFERROR(SUM(AQ10:AQ40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AQ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AR41" s="74">
-        <f>IFERROR(SUM(AR10:AR40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AR$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AS41" s="74">
-        <f>IFERROR(SUM(AS10:AS40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AS$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AT41" s="74">
-        <f>IFERROR(SUM(AT10:AT40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AT$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AU41" s="74">
-        <f>IFERROR(SUM(AU10:AU40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AU$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AV41" s="74">
-        <f>IFERROR(SUM(AV10:AV40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AV$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AW41" s="74">
-        <f>IFERROR(SUM(AW10:AW40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AW$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AX41" s="74">
-        <f>IFERROR(SUM(AX10:AX40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AX$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AY41" s="74">
-        <f>IFERROR(SUM(AY10:AY40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AY$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="AZ41" s="74">
-        <f>IFERROR(SUM(AZ10:AZ40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=AZ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BA41" s="74">
-        <f>IFERROR(SUM(BA10:BA40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BA$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BB41" s="74">
-        <f>IFERROR(SUM(BB10:BB40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BB$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BC41" s="74">
-        <f>IFERROR(SUM(BC10:BC40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BC$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BD41" s="74">
-        <f>IFERROR(SUM(BD10:BD40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BD$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BE41" s="74">
-        <f>IFERROR(SUM(BE10:BE40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BE$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BF41" s="74">
-        <f>IFERROR(SUM(BF10:BF40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BF$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BG41" s="74">
-        <f>IFERROR(SUM(BG10:BG40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BG$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BH41" s="74">
-        <f>IFERROR(SUM(BH10:BH40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BH$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BI41" s="74">
-        <f>IFERROR(SUM(BI10:BI40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BI$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BJ41" s="74">
-        <f>IFERROR(SUM(BJ10:BJ40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BJ$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BK41" s="74">
-        <f>IFERROR(SUM(BK10:BK40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BK$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
       <c r="BL41" s="74">
-        <f>IFERROR(SUM(BL10:BL40),0)</f>
+        <f>IFERROR(SUMPRODUCT((Payment_Data.$B$6:$B$100="VND-032")*(Payment_Data.$J$6:$J$100=BL$6)*(Payment_Data.$I$6:$I$100)),0)</f>
         <v/>
       </c>
     </row>
@@ -23475,6 +23326,22 @@
       <formula>E10&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E10:BN50">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="6">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="7">
+      <formula>100000</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="8">
+      <formula>500000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E50">
+    <cfRule type="expression" priority="10" dxfId="9">
+      <formula>OR($E$7="Fri",$E$7="Sat")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23753,7 +23620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24446,77 +24313,6 @@
       <c r="K28" s="35" t="n"/>
       <c r="L28" s="35" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -24531,7 +24327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25234,77 +25030,6 @@
       <c r="K28" s="35" t="n"/>
       <c r="L28" s="35" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -25319,7 +25044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25888,83 +25613,6 @@
       <c r="K22" s="35" t="n"/>
       <c r="L22" s="35" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -25979,7 +25627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -26735,76 +26383,6 @@
       <c r="K29" s="35" t="n"/>
       <c r="L29" s="35" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -26819,7 +26397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27415,82 +26993,6 @@
       <c r="K23" s="35" t="n"/>
       <c r="L23" s="35" t="n"/>
     </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -27505,7 +27007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28066,83 +27568,6 @@
       <c r="K22" s="35" t="n"/>
       <c r="L22" s="35" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
@@ -28157,7 +27582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28811,78 +28236,6 @@
       <c r="K27" s="35" t="n"/>
       <c r="L27" s="35" t="n"/>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
